--- a/enterprise/output/통합_고도화엔터프라이즈_보안위협_매트릭스_v1.xlsx
+++ b/enterprise/output/통합_고도화엔터프라이즈_보안위협_매트릭스_v1.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,9 +71,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <color rgb="008C8C8C"/>
     </font>
     <font>
       <b val="1"/>
@@ -204,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -226,9 +223,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -244,19 +238,19 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -275,6 +269,9 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -282,9 +279,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -915,7 +909,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>시트 양식만 — ③단계에서 작성</t>
+          <t>실제 사고 기반 공격 흐름 8개</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1089,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>0/51개 작성 — 문구는 ③단계 | validate.py 검증 생략(--skip-validate)</t>
+          <t>51/51개 작성 — 전 항목 완료 | validate.py 세부위협 51개(문구 51) · 사고 33건 · 시나리오 8개 · 실제 사고 매핑 행 45개 · 인용 사례 83건</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5123,7 +5117,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -5133,29 +5127,29 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>결정</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>작업방향 D5~D7·D9·D11·D12</t>
+          <t>워크북·CSV(scripts/build_enterprise_threat_matrix.py)</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>영역 2(고도화 엔터프라이즈 침해) 착수 결정 확정 — D5(ATT&amp;CK Enterprise에서 고도화·최근빈발·레거시난제 점수로 ~50행 선별, 자산 특화는 연계)·D6(Lv1 ATT&amp;CK 전술 + 레거시 공백 유형·요구 방어 수준 축)·D7(호스트·엔드포인트·네트워크·C2·회피·온프레미스 AD 인접, 클라우드·신원·OT·AI·공급망은 연계)·D9(통합본 뷰 Lv0)·D11(방어 자료 가드레일)·D12(v4.1 베이스라인)</t>
+          <t>15시트 워크북·CSV 생성(세부위협 51행). aiattack 빌드를 이식하되 레거시 공백·요구 방어 수준 고유 축 시트와 ATT&amp;CK·KEV 교차 시트를 둠. 위험도 매우 높음 17·높음 12·보통 21·낮음 1, 근거 수준 실제 사고 45·ATT&amp;CK/KEV 다수 3·일부 2·이론 1. 우선순위에 요구 방어 수준(방어 난이도)·ATT&amp;CK 주체 수 보조(D5). 빌드 전 검증기 자동 실행</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>emerging/작업방향 10장 권장안을 영역 2 착수 결정으로 확정</t>
+          <t>②단계(v1) — 분류·근거·평가를 한 워크북에서 검토</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -5165,29 +5159,29 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>구조</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>분류 체계(data/taxonomy.yaml)</t>
+          <t>관점 문구(data/text/*.yaml)</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>ATT&amp;CK Enterprise 침투~영향 12개 전술 도메인(IA·EX·PE·PV·DE·CA·DI·LM·CO·C2·EF·IM) → 위협분류 → 세부위협 51개 ID 대장(ENT-&lt;전술&gt;-NN). 전술 14개 중 정찰·자원 개발은 영역 1·정찰이 다뤄 제외·연계(D7). 행마다 레거시 방어 공백 유형·요구 방어 수준·주체·플랫폼·ATT&amp;CK·KEV·LOLBin·BYOVD 드라이버·대응 기준·연계·심각도. 심각도 상 26·중 24·하 1, 요구 방어 수준 '행위·네트워크·아이덴티티' 27·'EDR·XDR' 24</t>
+          <t>51개 행 전부에 핵심 요약·요약설명·참조(■ 관점·■ 실제 사례)·탐지·대응 작성. 인용 사례 83건([실제 사고]·[정부 경보]·[실증]), 실제 사고가 없는 5개 행(드라이브바이·네이티브 API·계정 조작·캐시 자격증명·보안 SW 탐색)은 '공개 사고 미확인 — 사유'로 표기. 가드레일 D11(공세 제작법 미기재, 탐지·대응 중심) 적용</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>D5·D6 확정안을 행 단위로 구현 — ①단계</t>
+          <t>③단계(v2) — 방어 관점으로 행마다 근거·통제를 연결</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -5197,29 +5191,29 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>시나리오</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>사고 DB(data/incidents.yaml)</t>
+          <t>공격 체인 시나리오(data/scenarios.yaml)</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>고도화·레거시 우회 침해 사고 33건 구축 — 경계·엣지 0-day(Citrix Bleed·MOVEit·Fortinet·Ivanti·Cisco IOS XE·PAN-OS·ScreenConnect·Cleo), 국가배후 LotL(Volt Typhoon·APT28 Nearest Neighbor), 사람 운영 랜섬웨어(Black Basta·Scattered Spider·Akira·LockBit·RansomHub), BYOVD EDR 킬러, 웜 확산(NotPetya·WannaCry), 커널·펌웨어(BlackLotus·루트킷·펌웨어 임플란트), C2·DNS·이동식 매체. 실제 사고가 매핑된 세부위협 45/51. CVE는 KEV 목록과 대조</t>
+          <t>실제 사고를 침해 흐름 8개로 재구성(ESN-01~08) — 엣지 0-day→LotL→확산, 사람 운영 랜섬웨어(BYOVD·복구 방해), 파일전송 0-day 갈취(Cl0p), 웜 확산→파괴, 비콘 C2, MSP 신뢰 관계, 지표 삭제 은닉, 커널·펌웨어 하위 계층. 21개 단계·초크 포인트 16개</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>D8 — 호스트·엔드포인트·네트워크·랜섬웨어·엣지 0-day 사례로 근거 구축</t>
+          <t>한 행=한 행위로 나눈 세부위협을 흐름 안에서 보고 차단 지점을 드러냄</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -5229,22 +5223,22 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>교차 매핑</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>프레임워크·참고 문헌(data/frameworks.yaml)</t>
+          <t>scripts/validate.py</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>ATT&amp;CK Enterprise v19.2(1차 분류·근거), CISA KEV 2026.10.02(1,733건), LOLBAS 245·LOLDrivers 706, NIST SP 800-53 Rev.5, 참고 문헌 카탈로그 8종(ATT&amp;CK·KEV·CISA·Mandiant·LOLBAS·LOLDrivers·Hive·Securelist)</t>
+          <t>문구·시나리오 검사 이식 — 형식, 사례 라벨↔집계 상태·시점·수치 대조, 참조 ID(ATT&amp;CK·CVE↔KEV·NIST·연계) 존재·행 매핑, 가드레일. 문구 51·시나리오 8을 --strict로 검증해 오류·경고 0</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>역할별 교차 매핑·근거 출처와 이용 조건을 행 매핑 전에 고정</t>
+          <t>문구·시나리오를 사고 DB·카탈로그와 기계적으로 대조</t>
         </is>
       </c>
     </row>
@@ -5261,22 +5255,22 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>결정</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>참조 추출본(reference/)</t>
+          <t>작업방향 D5~D7·D9·D11·D12</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>ATT&amp;CK 추출본(prepare_attack.py — 기법 68·주체 977·절차 6,087, 절차 수는 최근빈발 신호), KEV 추출본(prepare_kev.py — 연도별 등재·경계/엣지 장비 비중 15~21%·같은 해 악용 비중), LOLBAS·LOLDrivers 추출본(prepare_lolbas.py), NIST·통합 v4.1 연계 ID 237개(prepare_refs.py)</t>
+          <t>영역 2(고도화 엔터프라이즈 침해) 착수 결정 확정 — D5(ATT&amp;CK Enterprise에서 고도화·최근빈발·레거시난제 점수로 ~50행 선별, 자산 특화는 연계)·D6(Lv1 ATT&amp;CK 전술 + 레거시 공백 유형·요구 방어 수준 축)·D7(호스트·엔드포인트·네트워크·C2·회피·온프레미스 AD 인접, 클라우드·신원·OT·AI·공급망은 연계)·D9(통합본 뷰 Lv0)·D11(방어 자료 가드레일)·D12(v4.1 베이스라인)</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>빌드·검증을 저장소 안에서 재현. 겹치는 위협은 통합 v4.1 요약 ID로 연계만(D9)</t>
+          <t>emerging/작업방향 10장 권장안을 영역 2 착수 결정으로 확정</t>
         </is>
       </c>
     </row>
@@ -5293,20 +5287,148 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
+          <t>구조</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>분류 체계(data/taxonomy.yaml)</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>ATT&amp;CK Enterprise 침투~영향 12개 전술 도메인(IA·EX·PE·PV·DE·CA·DI·LM·CO·C2·EF·IM) → 위협분류 → 세부위협 51개 ID 대장(ENT-&lt;전술&gt;-NN). 전술 14개 중 정찰·자원 개발은 영역 1·정찰이 다뤄 제외·연계(D7). 행마다 레거시 방어 공백 유형·요구 방어 수준·주체·플랫폼·ATT&amp;CK·KEV·LOLBin·BYOVD 드라이버·대응 기준·연계·심각도. 심각도 상 26·중 24·하 1, 요구 방어 수준 '행위·네트워크·아이덴티티' 27·'EDR·XDR' 24</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>D5·D6 확정안을 행 단위로 구현 — ①단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>사고 DB(data/incidents.yaml)</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>고도화·레거시 우회 침해 사고 33건 구축 — 경계·엣지 0-day(Citrix Bleed·MOVEit·Fortinet·Ivanti·Cisco IOS XE·PAN-OS·ScreenConnect·Cleo), 국가배후 LotL(Volt Typhoon·APT28 Nearest Neighbor), 사람 운영 랜섬웨어(Black Basta·Scattered Spider·Akira·LockBit·RansomHub), BYOVD EDR 킬러, 웜 확산(NotPetya·WannaCry), 커널·펌웨어(BlackLotus·루트킷·펌웨어 임플란트), C2·DNS·이동식 매체. 실제 사고가 매핑된 세부위협 45/51. CVE는 KEV 목록과 대조</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>D8 — 호스트·엔드포인트·네트워크·랜섬웨어·엣지 0-day 사례로 근거 구축</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>교차 매핑</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>프레임워크·참고 문헌(data/frameworks.yaml)</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>ATT&amp;CK Enterprise v19.2(1차 분류·근거), CISA KEV 2026.10.02(1,733건), LOLBAS 245·LOLDrivers 706, NIST SP 800-53 Rev.5, 참고 문헌 카탈로그 8종(ATT&amp;CK·KEV·CISA·Mandiant·LOLBAS·LOLDrivers·Hive·Securelist)</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>역할별 교차 매핑·근거 출처와 이용 조건을 행 매핑 전에 고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>참조 추출본(reference/)</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>ATT&amp;CK 추출본(prepare_attack.py — 기법 68·주체 977·절차 6,087, 절차 수는 최근빈발 신호), KEV 추출본(prepare_kev.py — 연도별 등재·경계/엣지 장비 비중 15~21%·같은 해 악용 비중), LOLBAS·LOLDrivers 추출본(prepare_lolbas.py), NIST·통합 v4.1 연계 ID 237개(prepare_refs.py)</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>빌드·검증을 저장소 안에서 재현. 겹치는 위협은 통합 v4.1 요약 ID로 연계만(D9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
           <t>검증</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>scripts/validate.py · taxonomy_rules.py</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>검증기를 aiattack·물리 매트릭스 기준으로 이식 — 분류 체계 필드·어휘·ID 체계, ATT&amp;CK·KEV·NIST·연계·참고 문헌 키 존재, CVE↔KEV 대조, 레거시 공백·요구 방어 수준·주체·플랫폼 어휘, 사고 DB 필드·매핑·출처. 데이터 검증 오류·경고 0</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>①단계 완료 기준(매핑·참조 ID 전부 카탈로그에 존재, 검증 데이터 통과) 자동 확인</t>
         </is>
@@ -5441,12 +5563,12 @@
           <t>인터넷 노출 경계·엣지 장비 취약점 악용(빠른 n-day·0-day)</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exploitation of internet-facing edge/perimeter appliances</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>인터넷 노출 경계·엣지 장비 취약점으로 경계 안 직접 진입</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -5481,7 +5603,7 @@
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST RA-5·SI-2·SC-7·SI-4</t>
+          <t>외부 노출 자산을 지속 식별하고 엣지 장비의 취약점 공개·악용 동향을 신속 대조(NIST RA-5·SI-4)</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5626,12 @@
           <t>데이터 암호화(사람 운영 랜섬웨어)</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Data encrypted for impact (human-operated ransomware)</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>사람 운영 랜섬웨어의 도메인 장악 후 전사 암호화</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -5544,7 +5666,7 @@
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·CP-9·CP-10</t>
+          <t>대량 파일 변경·암호화 행위와 선행 단계(자격증명·확산) 상관 이벤트를 행위 기반으로 탐지(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -5567,12 +5689,12 @@
           <t>보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Impair/disable security tools (EDR tampering, BYOVD killers)</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>서명된 취약 드라이버로 EDR·백신을 커널에서 무력화(BYOVD)</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -5607,7 +5729,7 @@
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·SI-7·CM-7</t>
+          <t>보안 서비스 중지·드라이버 로드와 EDR 텔레메트리 단절을 행위·네트워크 기반으로 탐지(NIST SI-4·SI-7)</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5752,12 @@
           <t>원격 서비스 악용(RDP·SMB·WinRM)</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Remote services (RDP/SMB/WinRM)</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>정상 원격 서비스(RDP·SMB·WinRM)로 자격증명 써 확산</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -5670,7 +5792,7 @@
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AC-17·SI-4·SC-7</t>
+          <t>비정상 원격 세션(출발지·시간·계정)과 내부 RDP·SMB 급증을 네트워크·아이덴티티 기반으로 탐지(NIST SI-4·SC-7)</t>
         </is>
       </c>
     </row>
@@ -5693,12 +5815,12 @@
           <t>외부 원격 서비스 악용(VPN·RDP·원격 관리)</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exploitation/abuse of external remote services</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>탈취 계정·노출 원격 서비스로 정상 로그인처럼 경계 통과</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -5733,7 +5855,7 @@
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AC-17·IA-2·SC-7·SI-4</t>
+          <t>원격 서비스 로그인의 비정상 위치·시간·장치와 MFA 미적용 경로를 아이덴티티·네트워크 기반으로 탐지(NIST SI-4·IA-2)</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5878,12 @@
           <t>OS 자격증명 덤프(LSASS 메모리)</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) OS credential dumping (LSASS memory)</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>LSASS 메모리 덤프로 평문·해시 자격증명 탈취</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -5796,7 +5918,7 @@
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·AC-6·IA-5</t>
+          <t>LSASS 비정상 접근·핸들 열기와 자격증명 덤프 도구 행위를 EDR 기반으로 탐지(NIST SI-4·AC-6)</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5941,12 @@
           <t>PowerShell 악용(파일리스 실행)</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) PowerShell abuse (fileless execution)</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>PowerShell 파일리스 실행으로 시그니처 AV 무력화</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -5859,7 +5981,7 @@
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-3·SI-4·CM-7</t>
+          <t>PowerShell 스크립트 블록·명령줄 로깅과 비정상 실행 맥락(인코딩·다운로드·원격 실행)을 행위 기반으로 탐지(NIST SI-4·SI-3)</t>
         </is>
       </c>
     </row>
@@ -5882,12 +6004,12 @@
           <t>금전 탈취·이중 협박 갈취</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Financial theft / double-extortion</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>반출 데이터 공개 협박·부정 이체로 금전 피해 실현</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -5922,7 +6044,7 @@
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·IR-4</t>
+          <t>대량 반출 선행 징후와 갈취·부정 이체 정황을 통합 모니터링(NIST SI-4·IR-4)</t>
         </is>
       </c>
     </row>
@@ -5945,12 +6067,12 @@
           <t>정상 웹 서비스·대체 프로토콜 경유 반출</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exfiltration over web service / alternative protocol</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>정상 웹 서비스·대체 프로토콜로 대량 데이터 반출</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -5985,7 +6107,7 @@
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SC-7·SI-4</t>
+          <t>신뢰 SaaS·외부 저장소로의 비정상 대량 업로드를 네트워크·DLP 기반으로 탐지(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -6008,12 +6130,12 @@
           <t>C2 채널 경유 반출</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exfiltration over C2 channel</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>기존 암호화 C2 채널에 데이터 실어 반출</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -6048,7 +6170,7 @@
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SC-7·SI-4·AU-6</t>
+          <t>C2 세션의 비정상 업로드량·방향성과 비컨-대용량 전환을 네트워크 기반으로 탐지(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -6071,12 +6193,12 @@
           <t>대체 인증 자료 사용(Pass-the-Hash·Pass-the-Ticket)</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Use alternate authentication material (PtH/PtT)</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>대체 인증 자료(PtH·PtT)로 평문 없이 인증해 확산</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -6111,7 +6233,7 @@
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST IA-2·AC-6·SI-4</t>
+          <t>비정상 티켓·해시 사용과 로그온 유형·계정 불일치를 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)</t>
         </is>
       </c>
     </row>
@@ -6134,12 +6256,12 @@
           <t>신뢰 관계(MSP·협력사·연동) 악용</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Trusted relationship abuse</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>MSP·협력사·연동 신뢰 경로 악용으로 다수 하위 고객 침해</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -6174,7 +6296,7 @@
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AC-20·CA-3·SR-3·SI-4</t>
+          <t>신뢰 관계·연동 계정의 비정상 사용과 관리 도구발 대량·일괄 작업을 모니터링(NIST SI-4·AC-20)</t>
         </is>
       </c>
     </row>
@@ -6197,12 +6319,12 @@
           <t>Kerberoasting·AS-REP 로스팅</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Kerberoasting / AS-REP roasting</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Kerberoasting·AS-REP 로스팅으로 도메인 권한 계정 탈취</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -6237,7 +6359,7 @@
       </c>
       <c r="M17" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·AC-6·IA-5</t>
+          <t>비정상적으로 많은 서비스 티켓 요청·약한 암호화 요청을 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)</t>
         </is>
       </c>
     </row>
@@ -6260,12 +6382,12 @@
           <t>취약·악성 드라이버 로드(커널)</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Load vulnerable/malicious kernel driver</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>취약·악성 드라이버 로드로 커널 은닉·무력화 토대 마련</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -6300,7 +6422,7 @@
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-7·CM-7·SI-4</t>
+          <t>신규 커널 드라이버 로드와 취약 드라이버 서명·해시를 차단 목록과 대조(NIST SI-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6445,12 @@
           <t>서명된 정상 바이너리 프록시 실행(LOLBin)</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Signed binary proxy execution (LOLBins)</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>서명된 정상 바이너리(LOLBin) 대리 실행으로 허용 목록 통과</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -6363,7 +6485,7 @@
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST CM-7·SI-4·SI-7</t>
+          <t>정상 바이너리의 비정상 인자·부모 프로세스·네트워크 행위를 행위 기반으로 탐지(NIST SI-4·CM-7)</t>
         </is>
       </c>
     </row>
@@ -6386,12 +6508,12 @@
           <t>복구 방해(섀도 카피·백업 삭제)</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Inhibit system recovery</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>섀도 카피·백업 삭제로 복구 방해</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -6426,7 +6548,7 @@
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST CP-9·SI-4</t>
+          <t>섀도 카피 삭제·백업 서비스 중지 명령을 행위 기반으로 탐지(NIST SI-4·CP-9)</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6571,12 @@
           <t>원격 서비스 취약점 악용(웜 확산)</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exploitation of remote services (worm)</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>원격 서비스 취약점 악용으로 인증 없이 웜 확산</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -6489,7 +6611,7 @@
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST RA-5·SI-2·SC-7</t>
+          <t>내부 취약 서비스 대상 악용 시도와 급격한 횡적 전파를 네트워크 기반으로 탐지(NIST SC-7·RA-5)</t>
         </is>
       </c>
     </row>
@@ -6512,12 +6634,12 @@
           <t>도메인·AD 열거(계정·신뢰·공유)</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Domain/Active Directory enumeration</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>정상 LDAP·AD 질의로 공격 경로(관리자·신뢰·공유) 지도화</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -6552,7 +6674,7 @@
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·AC-6·AU-6</t>
+          <t>비정상 LDAP·AD 질의량과 공격 경로 지도화 도구 행위를 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)</t>
         </is>
       </c>
     </row>
@@ -6575,12 +6697,12 @@
           <t>지표 삭제(이벤트 로그·파일 삭제)</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Indicator removal (clear event logs, file deletion)</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>이벤트 로그·파일 삭제로 레거시 SIEM 탐지·분석 무력화</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -6615,7 +6737,7 @@
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AU-9·SI-4·AU-6</t>
+          <t>로그 삭제·감사 정책 변경 이벤트와 원격 수집 로그의 공백을 모니터링(NIST AU-6·SI-4)</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6760,12 @@
           <t>인그레스 도구 전송(페이로드 반입)</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Ingress tool transfer</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>정상 도구로 추가 페이로드 반입(인그레스 도구 전송)</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -6678,7 +6800,7 @@
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SC-7·SI-3·SI-4</t>
+          <t>정상 다운로드 도구의 비정상 사용·외부 다운로드를 행위·네트워크 기반으로 탐지(NIST SI-4·SC-7)</t>
         </is>
       </c>
     </row>
@@ -6701,12 +6823,12 @@
           <t>응용 계층 프로토콜(HTTPS) C2</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Application layer protocol (HTTPS) C2</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>응용 계층 프로토콜(HTTPS) C2로 포트·프로토콜 통제 통과</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -6741,7 +6863,7 @@
       </c>
       <c r="M25" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SC-7·SI-4·AU-6</t>
+          <t>HTTP(S) 비컨 주기·사용자 에이전트·목적지 이상을 네트워크 기반으로 탐지(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6886,12 @@
           <t>암호화 채널·비표준/정상 포트 위장 C2</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Encrypted channel / non-standard or common port C2</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>암호화 채널·비표준/정상 포트 위장으로 C2 식별 회피</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -6804,7 +6926,7 @@
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SC-7·SI-4·AU-6</t>
+          <t>TLS 메타데이터·JA3/비컨 주기·목적지 평판을 네트워크 기반으로 탐지(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -6827,12 +6949,12 @@
           <t>정상 웹 서비스·클라우드 플랫폼 경유 C2</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Web service / legitimate platform C2</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>정상 웹 서비스·클라우드 플랫폼을 C2 중계로 악용</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -6867,7 +6989,7 @@
       </c>
       <c r="M27" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SC-7·SI-4</t>
+          <t>신뢰 SaaS로의 비정상 API 호출·데이터량·주기를 네트워크 기반으로 탐지(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -6890,12 +7012,12 @@
           <t>데이터 파괴·와이퍼</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Data destruction / wiper</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>데이터 파괴·와이퍼로 운영 중단·복구 불능</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -6930,7 +7052,7 @@
       </c>
       <c r="M28" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-7·CP-9·SI-4</t>
+          <t>대량 삭제·디스크 와이프·MBR 변조 행위를 행위 기반으로 탐지(NIST SI-4·SI-7)</t>
         </is>
       </c>
     </row>
@@ -6953,12 +7075,12 @@
           <t>인메모리·반사 코드 로딩</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) In-memory / reflective code loading</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>인메모리·반사 코드 로딩으로 파일 기반 AV 원천 회피</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -6993,7 +7115,7 @@
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-3·SI-4</t>
+          <t>메모리 영역 할당·실행과 비정상 로딩을 EDR 메모리 스캔으로 탐지(NIST SI-3·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7016,12 +7138,12 @@
           <t>루트킷(사용자·커널 은폐)</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Rootkit</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>루트킷으로 프로세스·파일·연결을 하위 계층에서 은폐</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -7056,7 +7178,7 @@
       </c>
       <c r="M30" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-7·SI-4</t>
+          <t>커널 무결성·드라이버 서명과 메모리·부트 무결성 검증으로 은폐를 탐지(NIST SI-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7079,12 +7201,12 @@
           <t>프로세스 인젝션(인메모리 코드 주입)</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Process injection</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>프로세스 인젝션(인메모리 코드 주입)으로 실행·은닉·상승</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -7119,7 +7241,7 @@
       </c>
       <c r="M31" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-3·SI-4</t>
+          <t>원격 스레드 생성·메모리 쓰기·비정상 메모리 영역 실행을 EDR 행위 기반으로 탐지(NIST SI-3·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7142,12 +7264,12 @@
           <t>권한 상승 취약점 악용(로컬·커널)</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exploitation for privilege escalation</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>로컬·커널 취약점(또는 BYOVD)으로 SYSTEM·커널 권한 획득</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -7182,7 +7304,7 @@
       </c>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST RA-5·SI-2·SI-4</t>
+          <t>신규 커널 드라이버 로드와 취약 드라이버 서명·해시를 차단 목록과 대조해 탐지(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -7205,12 +7327,12 @@
           <t>펌웨어·부트킷(UEFI) 지속·은닉</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Pre-OS boot / firmware implant (bootkit)</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>펌웨어·부트킷(UEFI)으로 OS 아래 지속·은닉</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -7245,7 +7367,7 @@
       </c>
       <c r="M33" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-7·CM-7</t>
+          <t>펌웨어·부트 무결성 측정(보안 부팅·측정 부팅)과 펌웨어 버전·해시 변화를 점검(NIST SI-7)</t>
         </is>
       </c>
     </row>
@@ -7268,12 +7390,12 @@
           <t>Windows 관리 도구(WMI) 악용</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Windows Management Instrumentation abuse</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>Windows 관리 도구(WMI) 악용으로 파일리스 실행·이동</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -7308,7 +7430,7 @@
       </c>
       <c r="M34" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·CM-7·AU-6</t>
+          <t>WMI 이벤트 구독·원격 WMI 실행과 비정상 부모-자식 프로세스를 행위 기반으로 탐지(NIST SI-4·AU-6)</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7453,12 @@
           <t>도메인 프런팅·다단계 프록시</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Domain fronting / multi-hop proxy</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>도메인 프런팅·다단계 프록시로 도메인·IP 차단 우회</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -7371,7 +7493,7 @@
       </c>
       <c r="M35" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SC-7·SI-4</t>
+          <t>SNI와 실제 목적지 불일치·비정상 CDN 사용을 네트워크 기반으로 탐지(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7394,12 +7516,12 @@
           <t>DNS 경유 C2·터널링</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) DNS C2 / tunneling</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>DNS 경유 C2·터널링으로 방화벽 우회</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -7434,7 +7556,7 @@
       </c>
       <c r="M36" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SC-7·SI-4·AU-6</t>
+          <t>비정상 DNS 질의량·엔트로피·긴 서브도메인을 네트워크 기반으로 탐지(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7457,12 +7579,12 @@
           <t>호스트·시스템·네트워크 구성 탐색</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) System/host and network configuration discovery</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>정상 명령으로 호스트·시스템·네트워크 구성 탐색</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -7497,7 +7619,7 @@
       </c>
       <c r="M37" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·AU-6</t>
+          <t>짧은 시간의 연쇄 탐색 명령과 비정상 열거 패턴을 행위 기반으로 탐지(NIST SI-4·AU-6)</t>
         </is>
       </c>
     </row>
@@ -7520,12 +7642,12 @@
           <t>로컬·네트워크 공유 데이터 수집</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Data from local system and network shares</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>로컬·네트워크 공유에서 반출 대상 데이터 수집</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -7560,7 +7682,7 @@
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·AC-6</t>
+          <t>대량 파일 열람·공유 접근과 비정상 수집 패턴을 행위 기반으로 탐지(NIST SI-4·AC-6)</t>
         </is>
       </c>
     </row>
@@ -7583,12 +7705,12 @@
           <t>예약 작업(스케줄드 태스크)</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Scheduled task</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>예약 작업(스케줄드 태스크)으로 지속·주기 실행 확보</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -7623,7 +7745,7 @@
       </c>
       <c r="M39" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·CM-7·AU-6</t>
+          <t>신규·수정 예약 작업과 비정상 트리거·실행 바이너리를 행위 기반으로 탐지(NIST SI-4·AU-6)</t>
         </is>
       </c>
     </row>
@@ -7646,12 +7768,12 @@
           <t>파일·정보 난독화·암호화</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Obfuscated files or information</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>패킹·인코딩·암호화 난독화로 시그니처·정적 분석 회피</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -7686,7 +7808,7 @@
       </c>
       <c r="M40" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-3·SI-4</t>
+          <t>실행 시점 행위·언패킹과 비정상 인코딩·엔트로피를 행위 기반으로 탐지(NIST SI-3·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7709,12 +7831,12 @@
           <t>입력 캡처·키로깅</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Input capture / keylogging</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>입력 캡처·키로깅으로 자격증명 가로채기</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -7749,7 +7871,7 @@
       </c>
       <c r="M41" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·AC-6</t>
+          <t>키보드 후킹·입력 가로채기 API와 비정상 입력 캡처를 EDR 기반으로 탐지(NIST SI-4·AC-6)</t>
         </is>
       </c>
     </row>
@@ -7772,12 +7894,12 @@
           <t>윈도우 서비스 생성·수정</t>
         </is>
       </c>
-      <c r="E42" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Create or modify Windows service</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>윈도우 서비스 생성·수정으로 재부팅 후에도 접근 유지</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -7812,7 +7934,7 @@
       </c>
       <c r="M42" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·CM-7·AU-6</t>
+          <t>신규·수정 서비스와 비정상 바이너리 경로·시작 유형을 행위 기반으로 탐지(NIST SI-4·CM-7)</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7957,12 @@
           <t>서비스 중지·시스템 종료/재시작</t>
         </is>
       </c>
-      <c r="E43" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Service stop / system shutdown</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>보안·백업·DB 서비스 중지·시스템 종료로 가용성 훼손</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -7875,7 +7997,7 @@
       </c>
       <c r="M43" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·CP-10</t>
+          <t>보안·백업·DB 서비스의 비정상 중지와 대량 종료 명령을 행위 기반으로 탐지(NIST SI-4·CP-10)</t>
         </is>
       </c>
     </row>
@@ -7898,12 +8020,12 @@
           <t>수집 데이터 압축·암호화 스테이징</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Archive/stage collected data</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>수집 데이터 압축·암호화 스테이징으로 내용 검사 회피</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -7938,7 +8060,7 @@
       </c>
       <c r="M44" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·SC-7</t>
+          <t>대용량 압축·암호화 산출물 생성과 스테이징 디렉터리 집중을 행위 기반으로 탐지(NIST SI-4·SC-7)</t>
         </is>
       </c>
     </row>
@@ -7961,12 +8083,12 @@
           <t>사용자 계정 컨트롤(UAC) 우회</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Bypass User Account Control</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>사용자 계정 컨트롤(UAC) 우회로 로컬 권한 상승</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -8001,7 +8123,7 @@
       </c>
       <c r="M45" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AC-6·SI-4·CM-7</t>
+          <t>자동 상승 바이너리의 비정상 실행·레지스트리 조작을 행위 기반으로 탐지(NIST SI-4·CM-7)</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8146,12 @@
           <t>위장(정상 이름·경로·서명 가장)</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Masquerading</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>정상 이름·경로·서명 가장(위장)으로 눈·규칙 탐지 회피</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -8064,7 +8186,7 @@
       </c>
       <c r="M46" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·SI-7</t>
+          <t>정상 이름과 다른 경로·서명·해시 불일치를 무결성·행위 기반으로 탐지(NIST SI-4·SI-7)</t>
         </is>
       </c>
     </row>
@@ -8087,12 +8209,12 @@
           <t>측면 도구 전송</t>
         </is>
       </c>
-      <c r="E47" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Lateral tool transfer</t>
-        </is>
-      </c>
-      <c r="F47" s="14" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>측면 도구 전송으로 내부 공유·세션 통해 도구 확산</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -8127,7 +8249,7 @@
       </c>
       <c r="M47" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·SC-7</t>
+          <t>내부 호스트 간 비정상 파일 전송·공유 쓰기를 네트워크·엔드포인트 기반으로 탐지(NIST SI-4·SC-7)</t>
         </is>
       </c>
     </row>
@@ -8150,12 +8272,12 @@
           <t>이동식 매체·임시 접속 자산 경유 복제</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Replication through removable media</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>이동식 매체(USB)로 망분리·격리망 경계 우회 침투·전파</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -8190,7 +8312,7 @@
       </c>
       <c r="M48" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-3·MP-7·SC-7</t>
+          <t>이동식 매체 연결·자동 실행과 격리망 호스트의 비정상 실행을 엔드포인트 기반으로 탐지(NIST SI-3)</t>
         </is>
       </c>
     </row>
@@ -8213,12 +8335,12 @@
           <t>접근 토큰 조작</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Access token manipulation</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>접근 토큰 조작으로 다른 사용자 권한 사용</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -8253,7 +8375,7 @@
       </c>
       <c r="M49" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AC-6·SI-4</t>
+          <t>토큰 복제·가장 API 호출과 비정상 권한 전환을 EDR 행위 기반으로 탐지(NIST SI-4·AC-6)</t>
         </is>
       </c>
     </row>
@@ -8276,12 +8398,12 @@
           <t>부팅·로그온 자동 실행(레지스트리·시작 폴더)</t>
         </is>
       </c>
-      <c r="E50" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Boot or logon autostart execution</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>부팅·로그온 자동 실행(레지스트리·시작 폴더) 지속성</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -8316,7 +8438,7 @@
       </c>
       <c r="M50" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·SI-7·CM-7</t>
+          <t>자동 실행 지점(런키·시작 폴더·서비스)의 변경을 기준선과 대조해 탐지(NIST SI-4·SI-7)</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8461,12 @@
           <t>계정 조작·숨은 로컬 계정</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Account manipulation / hidden accounts</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>계정 조작·숨은 로컬 계정으로 신원 기반 지속 접근</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -8379,7 +8501,7 @@
       </c>
       <c r="M51" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AC-2·IA-4·AU-6</t>
+          <t>신규·변경 계정과 비정상 권한 부여·그룹 추가를 아이덴티티 기반으로 탐지(NIST AC-2·AU-6)</t>
         </is>
       </c>
     </row>
@@ -8402,12 +8524,12 @@
           <t>네이티브 API·시스템 서비스 실행</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Native API and system service execution</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>네이티브 API·시스템 서비스 직접 실행으로 후킹 탐지 회피</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -8442,7 +8564,7 @@
       </c>
       <c r="M52" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·CM-7</t>
+          <t>커널 콜백·시스템 서비스 생성과 비정상 API 호출 시퀀스를 EDR 행위 기반으로 탐지(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -8465,12 +8587,12 @@
           <t>드라이브바이 컴프로마이즈·워터링홀</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Drive-by compromise and watering hole</t>
-        </is>
-      </c>
-      <c r="F53" s="14" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>정상 사이트·광고망 경유 드라이브바이·워터링홀 감염</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -8505,7 +8627,7 @@
       </c>
       <c r="M53" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-3·SC-7·SI-4</t>
+          <t>엔드포인트의 브라우저·플러그인 비정상 실행과 신뢰 사이트발 악성 리다이렉트를 행위 기반으로 탐지(NIST SI-3·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8528,12 +8650,12 @@
           <t>캐시된 도메인 자격증명 추출</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Cached domain credentials</t>
-        </is>
-      </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>캐시된 도메인 자격증명 추출로 추가 계정 확보</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -8568,7 +8690,7 @@
       </c>
       <c r="M54" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·AC-6</t>
+          <t>캐시 자격증명 저장소 접근과 비정상 레지스트리·메모리 읽기를 EDR 기반으로 탐지(NIST SI-4·AC-6)</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8713,12 @@
           <t>보안 소프트웨어·방어 환경 탐색</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Security software discovery</t>
-        </is>
-      </c>
-      <c r="F55" s="15" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>보안 소프트웨어·방어 환경 탐색으로 회피 준비</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
@@ -8631,7 +8753,7 @@
       </c>
       <c r="M55" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4</t>
+          <t>보안 제품·서비스 열거 명령과 비정상 조회를 행위 기반으로 탐지(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -8672,84 +8794,84 @@
       </c>
     </row>
     <row r="2" ht="52" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>[IA] 초기 침투
 Initial Access
 (5)</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>[EX] 실행
 Execution
 (4)</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>[PE] 지속
 Persistence
 (4)</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>[PV] 권한 상승
 Privilege Escalation
 (4)</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>[DE] 방어 회피
 Defense Evasion
 (8)</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="15" t="inlineStr">
         <is>
           <t>[CA] 자격증명 접근
 Credential Access
 (4)</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>[DI] 탐색
 Discovery
 (3)</t>
         </is>
       </c>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="H2" s="15" t="inlineStr">
         <is>
           <t>[LM] 측면 이동
 Lateral Movement
 (4)</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="I2" s="15" t="inlineStr">
         <is>
           <t>[CO] 수집
 Collection
 (2)</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="J2" s="15" t="inlineStr">
         <is>
           <t>[C2] 명령·제어
 Command and Control
 (6)</t>
         </is>
       </c>
-      <c r="K2" s="16" t="inlineStr">
+      <c r="K2" s="15" t="inlineStr">
         <is>
           <t>[EF] 반출
 Exfiltration
 (2)</t>
         </is>
       </c>
-      <c r="L2" s="16" t="inlineStr">
+      <c r="L2" s="15" t="inlineStr">
         <is>
           <t>[IM] 영향
 Impact
@@ -8758,271 +8880,271 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>ENT-IA-01 인터넷 노출 경계·엣지 장비 취약점 악용(빠른 n-day·0-day) [8]</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>ENT-EX-01.1 PowerShell 악용(파일리스 실행) [3]</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>ENT-PE-01 윈도우 서비스 생성·수정 [1]</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>ENT-PV-01.1 프로세스 인젝션(인메모리 코드 주입) [1]</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>ENT-DE-01.1 보안 도구 무력화(EDR 변조·BYOVD EDR 킬러) [5]</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>ENT-CA-01.1 OS 자격증명 덤프(LSASS 메모리) [4]</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>ENT-DI-02 도메인·AD 열거(계정·신뢰·공유) [3]</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>ENT-LM-01 원격 서비스 악용(RDP·SMB·WinRM) [5]</t>
         </is>
       </c>
-      <c r="I3" s="18" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>ENT-CO-01 로컬·네트워크 공유 데이터 수집 [1]</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>ENT-C2-05 인그레스 도구 전송(페이로드 반입) [2]</t>
         </is>
       </c>
-      <c r="K3" s="17" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t>ENT-EF-02 정상 웹 서비스·대체 프로토콜 경유 반출 [3]</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t>ENT-IM-01 데이터 암호화(사람 운영 랜섬웨어) [7]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>ENT-IA-02 외부 원격 서비스 악용(VPN·RDP·원격 관리) [4]</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>ENT-EX-03 서명된 정상 바이너리 프록시 실행(LOLBin) [2]</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>ENT-PE-02 부팅·로그온 자동 실행(레지스트리·시작 폴더) [1]</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>ENT-PV-04 권한 상승 취약점 악용(로컬·커널) [1]</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>ENT-DE-01.2 취약·악성 드라이버 로드(커널) [2]</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>ENT-CA-03 Kerberoasting·AS-REP 로스팅 [2]</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>ENT-DI-01 호스트·시스템·네트워크 구성 탐색 [1]</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>ENT-LM-02 대체 인증 자료 사용(Pass-the-Hash·Pass-the-Ticket) [2]</t>
         </is>
       </c>
-      <c r="I4" s="18" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>ENT-CO-02 수집 데이터 압축·암호화 스테이징 [1]</t>
         </is>
       </c>
-      <c r="J4" s="19" t="inlineStr">
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>ENT-C2-01.1 암호화 채널·비표준/정상 포트 위장 C2 [1]</t>
         </is>
       </c>
-      <c r="K4" s="17" t="inlineStr">
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>ENT-EF-01 C2 채널 경유 반출 [2]</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="16" t="inlineStr">
         <is>
           <t>ENT-IM-05 금전 탈취·이중 협박 갈취 [3]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>ENT-IA-05 신뢰 관계(MSP·협력사·연동) 악용 [2]</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>ENT-EX-01.2 Windows 관리 도구(WMI) 악용 [1]</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>ENT-PE-03 예약 작업(스케줄드 태스크) [1]</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>ENT-PV-01.2 접근 토큰 조작 [1]</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>ENT-DE-03 지표 삭제(이벤트 로그·파일 삭제) [2]</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>ENT-CA-04 입력 캡처·키로깅 [1]</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>ENT-DI-03 보안 소프트웨어·방어 환경 탐색</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>ENT-LM-04 원격 서비스 취약점 악용(웜 확산) [2]</t>
         </is>
       </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>ENT-C2-01.2 응용 계층 프로토콜(HTTPS) C2 [1]</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="16" t="inlineStr">
         <is>
           <t>ENT-IM-02 복구 방해(섀도 카피·백업 삭제) [2]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>ENT-IA-04 이동식 매체·임시 접속 자산 경유 복제 [1]</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>ENT-EX-04 네이티브 API·시스템 서비스 실행</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>ENT-PE-04 계정 조작·숨은 로컬 계정</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>ENT-PV-03 사용자 계정 컨트롤(UAC) 우회 [1]</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>ENT-DE-06 인메모리·반사 코드 로딩 [1]</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>ENT-CA-01.2 캐시된 도메인 자격증명 추출</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>ENT-LM-03 측면 도구 전송 [1]</t>
         </is>
       </c>
-      <c r="J6" s="19" t="inlineStr">
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>ENT-C2-03 정상 웹 서비스·클라우드 플랫폼 경유 C2 [1]</t>
         </is>
       </c>
-      <c r="L6" s="19" t="inlineStr">
+      <c r="L6" s="18" t="inlineStr">
         <is>
           <t>ENT-IM-03 데이터 파괴·와이퍼 [1]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>ENT-IA-03 드라이브바이 컴프로마이즈·워터링홀</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>ENT-DE-07 루트킷(사용자·커널 은폐) [1]</t>
         </is>
       </c>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>ENT-C2-04 도메인 프런팅·다단계 프록시 [1]</t>
         </is>
       </c>
-      <c r="L7" s="18" t="inlineStr">
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>ENT-IM-04 서비스 중지·시스템 종료/재시작 [1]</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>ENT-DE-08 펌웨어·부트킷(UEFI) 지속·은닉</t>
         </is>
       </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>ENT-C2-06 DNS 경유 C2·터널링 [1]</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>ENT-DE-04 위장(정상 이름·경로·서명 가장) [1]</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>ENT-DE-05 파일·정보 난독화·암호화 [1]</t>
         </is>
@@ -9085,7 +9207,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>고도화 엔터프라이즈 침해 매트릭스 v1</t>
         </is>
@@ -9099,32 +9221,32 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>분류 체계</t>
         </is>
       </c>
-      <c r="I3" s="23" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>고유 축</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="23" t="inlineStr">
         <is>
           <t>교차 매핑</t>
         </is>
       </c>
-      <c r="Y3" s="25" t="inlineStr">
+      <c r="Y3" s="24" t="inlineStr">
         <is>
           <t>위험 평가</t>
         </is>
       </c>
-      <c r="AE3" s="26" t="inlineStr">
+      <c r="AE3" s="25" t="inlineStr">
         <is>
           <t>실제 근거</t>
         </is>
       </c>
-      <c r="AL3" s="27" t="inlineStr">
+      <c r="AL3" s="26" t="inlineStr">
         <is>
           <t>대응 기준·참고 문헌</t>
         </is>
@@ -9353,10 +9475,15 @@
           <t>인터넷 노출 경계·엣지 장비 취약점 악용(빠른 n-day·0-day)</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exploitation of internet-facing edge/perimeter appliances</t>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>인터넷 노출 경계·엣지 장비 취약점으로 경계 안 직접 진입</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 VPN·방화벽·게이트웨이·파일전송 같은 인터넷 노출 엣지 장비의 공개 즉시 악용되는 취약점으로 경계 안으로 바로 들어올 수 있음
+- 엣지 장비는 EDR이 깔리지 않아 레거시 경계 통제로 탐지가 어렵고, KEV 등재가 매년 15~21%를 차지할 만큼 빠른 n-day·0-day가 집중됨</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -9366,7 +9493,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -9429,7 +9556,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA5" s="12" t="inlineStr">
+      <c r="AA5" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -9459,7 +9586,7 @@
       <c r="AH5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" s="28" t="inlineStr">
+      <c r="AI5" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -9482,7 +9609,17 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM5" s="9" t="inlineStr"/>
+      <c r="AM5" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 외부 노출 자산을 지속 식별하고 엣지 장비의 취약점 공개·악용 동향을 신속 대조(NIST RA-5·SI-4)
+- 경계 장비의 비정상 설정 변경·세션·아웃바운드를 네트워크 기반으로 모니터링(NIST SC-7)
+■ 대응
+- 엣지 장비 신속 패치·가상 패치와 공개 취약점 노출 구간 최소화(NIST SI-2·RA-5)
+- 경계 장비를 분리·최소 노출하고 침해 전제의 세션 무효화·자격증명 교체 절차를 둠(NIST SC-7)
+- 참고: CISA 〈KEV Catalog〉 · CISA 〈Edge Device Advisory〉</t>
+        </is>
+      </c>
       <c r="AN5" s="9" t="inlineStr">
         <is>
           <t>CISA 〈KEV Catalog〉
@@ -9511,10 +9648,15 @@
           <t>외부 원격 서비스 악용(VPN·RDP·원격 관리)</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exploitation/abuse of external remote services</t>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>탈취 계정·노출 원격 서비스로 정상 로그인처럼 경계 통과</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취한 계정이나 노출된 VPN·RDP·원격 관리로 정상 인증처럼 경계를 통과해 들어올 수 있음
+- 로그인 자체는 정상이라 레거시가 악용과 구분하지 못하고, 랜섬웨어 초기 침투의 주 경로가 됨</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -9524,7 +9666,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -9587,7 +9729,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA6" s="12" t="inlineStr">
+      <c r="AA6" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -9617,7 +9759,7 @@
       <c r="AH6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI6" s="28" t="inlineStr">
+      <c r="AI6" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -9641,7 +9783,17 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM6" s="9" t="inlineStr"/>
+      <c r="AM6" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 원격 서비스 로그인의 비정상 위치·시간·장치와 MFA 미적용 경로를 아이덴티티·네트워크 기반으로 탐지(NIST SI-4·IA-2)
+- 노출 RDP·VPN·원격 관리 자산을 상시 식별(NIST SC-7)
+■ 대응
+- 모든 외부 원격 접근에 피싱 내성 MFA·조건부 접근을 적용하고 노출을 최소화(NIST AC-17·IA-2)
+- 원격 서비스 접근을 분리·제한하고 이상 로그인에 세션 차단(NIST SC-7)
+- 참고: Mandiant 〈M-Trends〉</t>
+        </is>
+      </c>
       <c r="AN6" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉
@@ -9670,10 +9822,15 @@
           <t>드라이브바이 컴프로마이즈·워터링홀</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Drive-by compromise and watering hole</t>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>정상 사이트·광고망 경유 드라이브바이·워터링홀 감염</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 사이트·광고망을 침해하거나 워터링홀로 꾸며 방문자 단말을 감염시킬 수 있음
+- 경계에서 걸러지지 않는 정상 트래픽을 경유해 레거시 통제를 우회하나, 피해는 후속 실행·확산 단계에서 커짐</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -9683,7 +9840,7 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -9738,7 +9895,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA7" s="14" t="inlineStr">
+      <c r="AA7" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9768,7 +9925,7 @@
       <c r="AH7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI7" s="29" t="inlineStr">
+      <c r="AI7" s="28" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 다수</t>
         </is>
@@ -9782,7 +9939,14 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM7" s="9" t="inlineStr"/>
+      <c r="AM7" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 엔드포인트의 브라우저·플러그인 비정상 실행과 신뢰 사이트발 악성 리다이렉트를 행위 기반으로 탐지(NIST SI-3·SI-4)
+■ 대응
+- 브라우저·플러그인 신속 패치, 웹 격리·콘텐츠 필터링과 엔드포인트 행위 탐지를 적용(NIST SI-3·SC-7)</t>
+        </is>
+      </c>
       <c r="AN7" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -9810,10 +9974,15 @@
           <t>이동식 매체·임시 접속 자산 경유 복제</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Replication through removable media</t>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>이동식 매체(USB)로 망분리·격리망 경계 우회 침투·전파</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 USB 등 이동식 매체로 망분리·격리망에 침투·전파해 네트워크 경계를 물리적으로 우회할 수 있음
+- 경계 통제 밖 경로라 레거시 네트워크 탐지가 보지 못하나 전파 속도·범위는 제한적임</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -9823,7 +9992,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -9882,7 +10051,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA8" s="14" t="inlineStr">
+      <c r="AA8" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9912,7 +10081,7 @@
       <c r="AH8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI8" s="28" t="inlineStr">
+      <c r="AI8" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -9934,7 +10103,14 @@
 SC-7 Boundary Protection</t>
         </is>
       </c>
-      <c r="AM8" s="9" t="inlineStr"/>
+      <c r="AM8" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 이동식 매체 연결·자동 실행과 격리망 호스트의 비정상 실행을 엔드포인트 기반으로 탐지(NIST SI-3)
+■ 대응
+- 이동식 매체 사용을 통제·차단하고 자동 실행을 비활성화, 격리망 자산 반입 매체를 검사(NIST MP-7·SI-3)</t>
+        </is>
+      </c>
       <c r="AN8" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -9962,10 +10138,15 @@
           <t>신뢰 관계(MSP·협력사·연동) 악용</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Trusted relationship abuse</t>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>MSP·협력사·연동 신뢰 경로 악용으로 다수 하위 고객 침해</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 MSP·원격 관리·연동 토큰 같은 신뢰 관계로 들어와 다수 하위 고객을 한 번에 침해할 수 있음
+- 정상 관리 트래픽을 경유해 레거시가 구분하지 못하고 피해가 연쇄됨</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -9975,7 +10156,7 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -10034,7 +10215,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA9" s="12" t="inlineStr">
+      <c r="AA9" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -10064,7 +10245,7 @@
       <c r="AH9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI9" s="28" t="inlineStr">
+      <c r="AI9" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -10087,7 +10268,15 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM9" s="9" t="inlineStr"/>
+      <c r="AM9" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신뢰 관계·연동 계정의 비정상 사용과 관리 도구발 대량·일괄 작업을 모니터링(NIST SI-4·AC-20)
+■ 대응
+- 공급·관리 관계에 최소 권한·분리·계약상 보안 요구를 적용하고 연동 토큰을 단기화·감사(NIST SR-3·CA-3·AC-20)
+- 참고: Mandiant 〈M-Trends〉</t>
+        </is>
+      </c>
       <c r="AN9" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉
@@ -10116,10 +10305,15 @@
           <t>PowerShell 악용(파일리스 실행)</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) PowerShell abuse (fileless execution)</t>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>PowerShell 파일리스 실행으로 시그니처 AV 무력화</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 PowerShell로 디스크에 파일을 남기지 않고 메모리에서 코드를 실행할 수 있음
+- 시그니처 AV가 보지 못해 행위 맥락으로만 탐지되며, 사람 운영 랜섬웨어·국가배후 작전의 기본 실행 수단임</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -10129,7 +10323,7 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
@@ -10188,7 +10382,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA10" s="12" t="inlineStr">
+      <c r="AA10" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -10218,7 +10412,7 @@
       <c r="AH10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI10" s="28" t="inlineStr">
+      <c r="AI10" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -10240,7 +10434,15 @@
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AM10" s="9" t="inlineStr"/>
+      <c r="AM10" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- PowerShell 스크립트 블록·명령줄 로깅과 비정상 실행 맥락(인코딩·다운로드·원격 실행)을 행위 기반으로 탐지(NIST SI-4·SI-3)
+■ 대응
+- 스크립트 로깅·제약 언어 모드·서명 정책과 최소 기능 원칙을 적용(NIST CM-7·SI-4)
+- 참고: LOLBAS 〈Project〉</t>
+        </is>
+      </c>
       <c r="AN10" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉
@@ -10269,10 +10471,15 @@
           <t>Windows 관리 도구(WMI) 악용</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Windows Management Instrumentation abuse</t>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Windows 관리 도구(WMI) 악용으로 파일리스 실행·이동</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 WMI 같은 정상 관리 기능으로 파일 없이 실행·측면 이동·수집을 수행할 수 있음
+- 정상 관리 트래픽이라 레거시가 구분하지 못하나 단독 피해보다 다른 단계를 잇는 수단임</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -10282,7 +10489,7 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -10337,7 +10544,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA11" s="14" t="inlineStr">
+      <c r="AA11" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -10367,7 +10574,7 @@
       <c r="AH11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" s="28" t="inlineStr">
+      <c r="AI11" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -10389,7 +10596,14 @@
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM11" s="9" t="inlineStr"/>
+      <c r="AM11" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- WMI 이벤트 구독·원격 WMI 실행과 비정상 부모-자식 프로세스를 행위 기반으로 탐지(NIST SI-4·AU-6)
+■ 대응
+- WMI 원격 실행을 제한하고 관리 활동을 기준선과 대조·감사(NIST CM-7·AU-6)</t>
+        </is>
+      </c>
       <c r="AN11" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -10417,10 +10631,15 @@
           <t>서명된 정상 바이너리 프록시 실행(LOLBin)</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Signed binary proxy execution (LOLBins)</t>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>서명된 정상 바이너리(LOLBin) 대리 실행으로 허용 목록 통과</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 OS에 서명·내장된 정상 바이너리로 악성 코드를 대리 실행하거나 페이로드를 내려받을 수 있음
+- 허용 목록·서명 검증을 통과해 레거시 통제가 구분하지 못함(LOLBAS 245개 수록)</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -10430,7 +10649,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -10489,7 +10708,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA12" s="12" t="inlineStr">
+      <c r="AA12" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -10519,7 +10738,7 @@
       <c r="AH12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI12" s="28" t="inlineStr">
+      <c r="AI12" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -10542,7 +10761,15 @@
 SI-7 Software, Firmware, and Information Integrity</t>
         </is>
       </c>
-      <c r="AM12" s="9" t="inlineStr"/>
+      <c r="AM12" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 정상 바이너리의 비정상 인자·부모 프로세스·네트워크 행위를 행위 기반으로 탐지(NIST SI-4·CM-7)
+■ 대응
+- 불필요한 LOLBin 실행을 허용 목록·애플리케이션 제어로 제한하고 무결성·실행 맥락을 감시(NIST CM-7·SI-7)
+- 참고: LOLBAS 〈Project〉</t>
+        </is>
+      </c>
       <c r="AN12" s="9" t="inlineStr">
         <is>
           <t>LOLBAS 〈Project〉
@@ -10571,10 +10798,15 @@
           <t>네이티브 API·시스템 서비스 실행</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr"/>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Native API and system service execution</t>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>네이티브 API·시스템 서비스 직접 실행으로 후킹 탐지 회피</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 네이티브 API를 직접 호출하거나 시스템 서비스로 실행해 중간 도구를 거치지 않을 수 있음
+- 후킹 기반 탐지를 우회하나 피해는 후속 단계에서 발생함</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -10584,7 +10816,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -10640,7 +10872,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA13" s="14" t="inlineStr">
+      <c r="AA13" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -10670,7 +10902,7 @@
       <c r="AH13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI13" s="29" t="inlineStr">
+      <c r="AI13" s="28" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 다수</t>
         </is>
@@ -10683,7 +10915,14 @@
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AM13" s="9" t="inlineStr"/>
+      <c r="AM13" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 커널 콜백·시스템 서비스 생성과 비정상 API 호출 시퀀스를 EDR 행위 기반으로 탐지(NIST SI-4)
+■ 대응
+- 커널 수준 가시성(EDR)과 최소 기능·서비스 생성 통제를 적용(NIST CM-7·SI-4)</t>
+        </is>
+      </c>
       <c r="AN13" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -10711,10 +10950,15 @@
           <t>윈도우 서비스 생성·수정</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr"/>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Create or modify Windows service</t>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>윈도우 서비스 생성·수정으로 재부팅 후에도 접근 유지</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 서비스 등록 메커니즘으로 서비스를 만들거나 바꿔 지속·권한 상승에 쓸 수 있음
+- 정상 OS 기능이라 레거시가 악용과 구분하기 어려우나 단독 피해는 제한적임</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -10724,7 +10968,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -10779,7 +11023,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA14" s="14" t="inlineStr">
+      <c r="AA14" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -10809,7 +11053,7 @@
       <c r="AH14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI14" s="28" t="inlineStr">
+      <c r="AI14" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -10831,7 +11075,14 @@
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM14" s="9" t="inlineStr"/>
+      <c r="AM14" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규·수정 서비스와 비정상 바이너리 경로·시작 유형을 행위 기반으로 탐지(NIST SI-4·CM-7)
+■ 대응
+- 서비스 생성·변경을 감사·기준선과 대조하고 최소 권한을 적용(NIST CM-7·AU-6)</t>
+        </is>
+      </c>
       <c r="AN14" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -10859,10 +11110,15 @@
           <t>부팅·로그온 자동 실행(레지스트리·시작 폴더)</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Boot or logon autostart execution</t>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>부팅·로그온 자동 실행(레지스트리·시작 폴더) 지속성</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 레지스트리 런키·시작 폴더 등 자동 실행 지점에 등록해 재부팅·로그온 시 접근을 유지할 수 있음
+- 정상 자동 실행 메커니즘이라 레거시가 구분하기 어렵고 피해는 후속 단계에서 발생함</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -10872,7 +11128,7 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -10927,7 +11183,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA15" s="14" t="inlineStr">
+      <c r="AA15" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -10957,7 +11213,7 @@
       <c r="AH15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI15" s="28" t="inlineStr">
+      <c r="AI15" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -10979,7 +11235,14 @@
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AM15" s="9" t="inlineStr"/>
+      <c r="AM15" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자동 실행 지점(런키·시작 폴더·서비스)의 변경을 기준선과 대조해 탐지(NIST SI-4·SI-7)
+■ 대응
+- 자동 실행 지점 변경을 감사·무결성 검증하고 최소 기능을 적용(NIST CM-7·SI-7)</t>
+        </is>
+      </c>
       <c r="AN15" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -11007,10 +11270,15 @@
           <t>예약 작업(스케줄드 태스크)</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr"/>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Scheduled task</t>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>예약 작업(스케줄드 태스크)으로 지속·주기 실행 확보</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 스케줄러로 예약 작업을 만들어 지속성과 주기 실행을 확보할 수 있음
+- 정상 기능이라 레거시가 구분하기 어려우나 단독 피해는 제한적임</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -11020,7 +11288,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
@@ -11075,7 +11343,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA16" s="14" t="inlineStr">
+      <c r="AA16" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -11105,7 +11373,7 @@
       <c r="AH16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI16" s="28" t="inlineStr">
+      <c r="AI16" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -11127,7 +11395,14 @@
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM16" s="9" t="inlineStr"/>
+      <c r="AM16" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규·수정 예약 작업과 비정상 트리거·실행 바이너리를 행위 기반으로 탐지(NIST SI-4·AU-6)
+■ 대응
+- 예약 작업 생성·변경을 감사하고 생성 권한을 최소화(NIST CM-7·AU-6)</t>
+        </is>
+      </c>
       <c r="AN16" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -11155,10 +11430,15 @@
           <t>계정 조작·숨은 로컬 계정</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr"/>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Account manipulation / hidden accounts</t>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>계정 조작·숨은 로컬 계정으로 신원 기반 지속 접근</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 계정·권한을 추가·변경하거나 숨은 로컬 계정을 만들어 지속 접근을 확보할 수 있음
+- 정상 계정 활동으로 보여 로그만으로는 악용을 구분하기 어려움</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -11168,7 +11448,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -11227,7 +11507,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA17" s="14" t="inlineStr">
+      <c r="AA17" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -11257,7 +11537,7 @@
       <c r="AH17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI17" s="30" t="inlineStr">
+      <c r="AI17" s="29" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 일부</t>
         </is>
@@ -11271,7 +11551,14 @@
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM17" s="9" t="inlineStr"/>
+      <c r="AM17" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규·변경 계정과 비정상 권한 부여·그룹 추가를 아이덴티티 기반으로 탐지(NIST AC-2·AU-6)
+■ 대응
+- 계정 생성·권한 변경을 승인·감사하고 휴면·불필요 계정을 정리(NIST AC-2·IA-4)</t>
+        </is>
+      </c>
       <c r="AN17" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -11299,10 +11586,15 @@
           <t>프로세스 인젝션(인메모리 코드 주입)</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr"/>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Process injection</t>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>프로세스 인젝션(인메모리 코드 주입)으로 실행·은닉·상승</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 프로세스 메모리에 코드를 주입해 실행·은닉하고 권한을 높일 수 있음
+- 디스크 산출물이 없어 시그니처가 보지 못하며 거의 모든 고급 악성코드가 사용함</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -11312,7 +11604,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
@@ -11367,7 +11659,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA18" s="13" t="inlineStr">
+      <c r="AA18" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -11397,7 +11689,7 @@
       <c r="AH18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI18" s="28" t="inlineStr">
+      <c r="AI18" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -11418,7 +11710,14 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM18" s="9" t="inlineStr"/>
+      <c r="AM18" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 원격 스레드 생성·메모리 쓰기·비정상 메모리 영역 실행을 EDR 행위 기반으로 탐지(NIST SI-3·SI-4)
+■ 대응
+- 커널 수준 메모리 가시성(EDR)과 공격 표면 축소 규칙을 적용(NIST SI-3·SI-4)</t>
+        </is>
+      </c>
       <c r="AN18" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -11446,10 +11745,15 @@
           <t>접근 토큰 조작</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr"/>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Access token manipulation</t>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>접근 토큰 조작으로 다른 사용자 권한 사용</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 토큰을 복제·가장해 다른 사용자·서비스 권한으로 행동할 수 있음
+- 정상 인증 메커니즘을 써 레거시가 구분하기 어려우나 피해는 후속 단계에서 커짐</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -11459,7 +11763,7 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
@@ -11514,7 +11818,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA19" s="14" t="inlineStr">
+      <c r="AA19" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -11544,7 +11848,7 @@
       <c r="AH19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" s="28" t="inlineStr">
+      <c r="AI19" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -11565,7 +11869,14 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM19" s="9" t="inlineStr"/>
+      <c r="AM19" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 토큰 복제·가장 API 호출과 비정상 권한 전환을 EDR 행위 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- 최소 권한·특권 계정 분리와 토큰 조작 탐지 규칙을 적용(NIST AC-6·SI-4)</t>
+        </is>
+      </c>
       <c r="AN19" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -11593,10 +11904,15 @@
           <t>사용자 계정 컨트롤(UAC) 우회</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr"/>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Bypass User Account Control</t>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>사용자 계정 컨트롤(UAC) 우회로 로컬 권한 상승</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 자동 상승 바이너리를 악용해 UAC를 우회하고 관리자 권한을 얻을 수 있음
+- 정상 메커니즘을 써 레거시가 구분하기 어려우나 단독 피해는 제한적임</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -11606,7 +11922,7 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -11661,7 +11977,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA20" s="14" t="inlineStr">
+      <c r="AA20" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -11691,7 +12007,7 @@
       <c r="AH20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI20" s="28" t="inlineStr">
+      <c r="AI20" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -11713,7 +12029,14 @@
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AM20" s="9" t="inlineStr"/>
+      <c r="AM20" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자동 상승 바이너리의 비정상 실행·레지스트리 조작을 행위 기반으로 탐지(NIST SI-4·CM-7)
+■ 대응
+- UAC 최고 수준 설정·관리자 승인 모드와 최소 권한을 적용(NIST AC-6·CM-7)</t>
+        </is>
+      </c>
       <c r="AN20" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -11741,10 +12064,15 @@
           <t>권한 상승 취약점 악용(로컬·커널)</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr"/>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exploitation for privilege escalation</t>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>로컬·커널 취약점(또는 BYOVD)으로 SYSTEM·커널 권한 획득</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 로컬·커널 취약점이나 서명된 취약 드라이버(BYOVD)로 SYSTEM·커널 권한을 얻을 수 있음
+- 하위 계층이라 상위 보안 도구가 무력화되고 KEV 등재가 다수임</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -11754,7 +12082,7 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -11817,7 +12145,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA21" s="13" t="inlineStr">
+      <c r="AA21" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -11847,7 +12175,7 @@
       <c r="AH21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI21" s="28" t="inlineStr">
+      <c r="AI21" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -11869,7 +12197,15 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM21" s="9" t="inlineStr"/>
+      <c r="AM21" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 커널 드라이버 로드와 취약 드라이버 서명·해시를 차단 목록과 대조해 탐지(NIST SI-4)
+■ 대응
+- 취약 드라이버 차단 목록(HVCI·드라이버 블록리스트)과 신속 패치를 적용(NIST SI-2·SI-4)
+- 참고: LOLDrivers 〈Project〉</t>
+        </is>
+      </c>
       <c r="AN21" s="9" t="inlineStr">
         <is>
           <t>CISA 〈KEV Catalog〉
@@ -11898,10 +12234,15 @@
           <t>보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Impair/disable security tools (EDR tampering, BYOVD killers)</t>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>서명된 취약 드라이버로 EDR·백신을 커널에서 무력화(BYOVD)</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 서명된 취약 드라이버를 올려 EDR·백신을 커널에서 무력화할 수 있음
+- 보안 도구 자체가 꺼지므로 이후 단계가 전부 가려지고, 여러 랜섬웨어·국가배후가 EDR 킬러를 공유함</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -11911,7 +12252,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -11971,7 +12312,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA22" s="12" t="inlineStr">
+      <c r="AA22" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -12001,7 +12342,7 @@
       <c r="AH22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI22" s="28" t="inlineStr">
+      <c r="AI22" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -12024,7 +12365,15 @@
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AM22" s="9" t="inlineStr"/>
+      <c r="AM22" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 보안 서비스 중지·드라이버 로드와 EDR 텔레메트리 단절을 행위·네트워크 기반으로 탐지(NIST SI-4·SI-7)
+■ 대응
+- 취약 드라이버 차단 목록(HVCI·블록리스트)·변조 방지와 보안 도구 상태를 중앙 감시(NIST SI-7·CM-7)
+- 참고: LOLDrivers 〈Project〉 · Hive Security 〈Modern Attack Techniques 2026〉</t>
+        </is>
+      </c>
       <c r="AN22" s="9" t="inlineStr">
         <is>
           <t>LOLDrivers 〈Project〉
@@ -12053,10 +12402,15 @@
           <t>취약·악성 드라이버 로드(커널)</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Load vulnerable/malicious kernel driver</t>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>취약·악성 드라이버 로드로 커널 은닉·무력화 토대 마련</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 취약·악성 드라이버를 커널에 올려 은닉·무력화의 토대를 만들 수 있음
+- 커널 계층이라 상위 보안 제품이 보지 못함</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -12066,7 +12420,7 @@
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
@@ -12125,7 +12479,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA23" s="12" t="inlineStr">
+      <c r="AA23" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -12155,7 +12509,7 @@
       <c r="AH23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" s="28" t="inlineStr">
+      <c r="AI23" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -12177,7 +12531,15 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM23" s="9" t="inlineStr"/>
+      <c r="AM23" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 커널 드라이버 로드와 취약 드라이버 서명·해시를 차단 목록과 대조(NIST SI-7·SI-4)
+■ 대응
+- HVCI·드라이버 블록리스트로 취약 드라이버 로드를 차단(NIST SI-7·CM-7)
+- 참고: LOLDrivers 〈Project〉</t>
+        </is>
+      </c>
       <c r="AN23" s="9" t="inlineStr">
         <is>
           <t>LOLDrivers 〈Project〉</t>
@@ -12205,10 +12567,15 @@
           <t>지표 삭제(이벤트 로그·파일 삭제)</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr"/>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Indicator removal (clear event logs, file deletion)</t>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>이벤트 로그·파일 삭제로 레거시 SIEM 탐지·분석 무력화</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 이벤트 로그·파일을 지워 레거시 SIEM 탐지와 사후 분석을 무력화할 수 있음
+- 원격·불변 로그가 없으면 흔적이 사라져 추적이 어려워짐</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -12218,7 +12585,7 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
@@ -12275,7 +12642,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA24" s="13" t="inlineStr">
+      <c r="AA24" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -12305,7 +12672,7 @@
       <c r="AH24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI24" s="28" t="inlineStr">
+      <c r="AI24" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -12327,7 +12694,14 @@
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM24" s="9" t="inlineStr"/>
+      <c r="AM24" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 로그 삭제·감사 정책 변경 이벤트와 원격 수집 로그의 공백을 모니터링(NIST AU-6·SI-4)
+■ 대응
+- 원격·불변 로그 전송과 로그 삭제 방지·보존 정책을 적용(NIST AU-9·AU-6)</t>
+        </is>
+      </c>
       <c r="AN24" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -12355,10 +12729,15 @@
           <t>위장(정상 이름·경로·서명 가장)</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Masquerading</t>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>정상 이름·경로·서명 가장(위장)으로 눈·규칙 탐지 회피</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 프로세스·경로·서명으로 위장해 사람 눈과 규칙 기반 탐지를 피할 수 있음
+- 정상처럼 보여 레거시가 구분하기 어려우나 단독 피해는 제한적임</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
@@ -12368,7 +12747,7 @@
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
@@ -12423,7 +12802,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA25" s="14" t="inlineStr">
+      <c r="AA25" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -12453,7 +12832,7 @@
       <c r="AH25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI25" s="28" t="inlineStr">
+      <c r="AI25" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -12474,7 +12853,14 @@
 SI-7 Software, Firmware, and Information Integrity</t>
         </is>
       </c>
-      <c r="AM25" s="9" t="inlineStr"/>
+      <c r="AM25" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 정상 이름과 다른 경로·서명·해시 불일치를 무결성·행위 기반으로 탐지(NIST SI-4·SI-7)
+■ 대응
+- 바이너리 무결성·서명 검증과 정상 경로 기준선 대조를 적용(NIST SI-7·SI-4)</t>
+        </is>
+      </c>
       <c r="AN25" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -12502,10 +12888,15 @@
           <t>파일·정보 난독화·암호화</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr"/>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Obfuscated files or information</t>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>패킹·인코딩·암호화 난독화로 시그니처·정적 분석 회피</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 페이로드를 패킹·인코딩·암호화해 시그니처·정적 분석을 회피할 수 있음
+- 변종 양산으로 레거시 AV를 지속 우회하나 단독 피해는 제한적임</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -12515,7 +12906,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
@@ -12570,7 +12961,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA26" s="14" t="inlineStr">
+      <c r="AA26" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -12600,7 +12991,7 @@
       <c r="AH26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI26" s="28" t="inlineStr">
+      <c r="AI26" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -12621,7 +13012,14 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM26" s="9" t="inlineStr"/>
+      <c r="AM26" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 실행 시점 행위·언패킹과 비정상 인코딩·엔트로피를 행위 기반으로 탐지(NIST SI-3·SI-4)
+■ 대응
+- 시그니처 의존을 줄이고 행위 기반·샌드박스 분석을 병행(NIST SI-3·SI-4)</t>
+        </is>
+      </c>
       <c r="AN26" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -12649,10 +13047,15 @@
           <t>인메모리·반사 코드 로딩</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr"/>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) In-memory / reflective code loading</t>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>인메모리·반사 코드 로딩으로 파일 기반 AV 원천 회피</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 디스크를 거치지 않고 메모리에서 페이로드를 로드·실행할 수 있음
+- 파일 기반 AV·시그니처가 원천적으로 보지 못해 행위·메모리 기반 탐지가 필요함</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -12662,7 +13065,7 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
@@ -12717,7 +13120,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA27" s="13" t="inlineStr">
+      <c r="AA27" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -12747,7 +13150,7 @@
       <c r="AH27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI27" s="28" t="inlineStr">
+      <c r="AI27" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -12768,7 +13171,14 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM27" s="9" t="inlineStr"/>
+      <c r="AM27" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 메모리 영역 할당·실행과 비정상 로딩을 EDR 메모리 스캔으로 탐지(NIST SI-3·SI-4)
+■ 대응
+- 메모리 가시성(EDR)·공격 표면 축소와 스크립트 실행 통제를 적용(NIST SI-3·SI-4)</t>
+        </is>
+      </c>
       <c r="AN27" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -12796,10 +13206,15 @@
           <t>루트킷(사용자·커널 은폐)</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr"/>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Rootkit</t>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>루트킷으로 프로세스·파일·연결을 하위 계층에서 은폐</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 루트킷으로 프로세스·파일·연결을 하위 계층에서 숨겨 탐지·분석을 방해할 수 있음
+- 레거시로는 존재 자체를 알기 어려워 장기 잠복에 쓰임</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -12809,7 +13224,7 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
@@ -12864,7 +13279,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA28" s="13" t="inlineStr">
+      <c r="AA28" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -12894,7 +13309,7 @@
       <c r="AH28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI28" s="28" t="inlineStr">
+      <c r="AI28" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -12915,7 +13330,14 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM28" s="9" t="inlineStr"/>
+      <c r="AM28" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 커널 무결성·드라이버 서명과 메모리·부트 무결성 검증으로 은폐를 탐지(NIST SI-7·SI-4)
+■ 대응
+- 커널 무결성 보호(HVCI)·보안 부팅과 하위 계층 텔레메트리를 확보(NIST SI-7·SI-4)</t>
+        </is>
+      </c>
       <c r="AN28" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -12943,10 +13365,15 @@
           <t>펌웨어·부트킷(UEFI) 지속·은닉</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr"/>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Pre-OS boot / firmware implant (bootkit)</t>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>펌웨어·부트킷(UEFI)으로 OS 아래 지속·은닉</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 OS 아래 펌웨어·부트 단계에 임플란트를 심어 재설치·디스크 교체에도 지속할 수 있음
+- OS 보안 제품의 가시성 밖이라 레거시·EDR 모두 사실상 공백임</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -12956,7 +13383,7 @@
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
@@ -13011,7 +13438,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA29" s="13" t="inlineStr">
+      <c r="AA29" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -13041,7 +13468,7 @@
       <c r="AH29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI29" s="31" t="inlineStr">
+      <c r="AI29" s="30" t="inlineStr">
         <is>
           <t>이론·연구</t>
         </is>
@@ -13059,7 +13486,14 @@
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AM29" s="9" t="inlineStr"/>
+      <c r="AM29" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 펌웨어·부트 무결성 측정(보안 부팅·측정 부팅)과 펌웨어 버전·해시 변화를 점검(NIST SI-7)
+■ 대응
+- 보안 부팅·펌웨어 무결성 검증·업데이트와 펌웨어 공급 신뢰를 관리(NIST SI-7·CM-7)</t>
+        </is>
+      </c>
       <c r="AN29" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -13087,10 +13521,15 @@
           <t>OS 자격증명 덤프(LSASS 메모리)</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr"/>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) OS credential dumping (LSASS memory)</t>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>LSASS 메모리 덤프로 평문·해시 자격증명 탈취</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 LSASS 메모리에서 평문·해시 자격증명을 추출해 도메인 확산의 발판을 마련할 수 있음
+- 정상 프로세스 접근이라 레거시가 구분하지 못해 행위·EDR 기반 탐지가 필요함</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -13100,7 +13539,7 @@
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I30" s="9" t="inlineStr">
@@ -13155,7 +13594,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA30" s="12" t="inlineStr">
+      <c r="AA30" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -13185,7 +13624,7 @@
       <c r="AH30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI30" s="28" t="inlineStr">
+      <c r="AI30" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -13208,7 +13647,14 @@
 IA-5 Authenticator Management</t>
         </is>
       </c>
-      <c r="AM30" s="9" t="inlineStr"/>
+      <c r="AM30" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- LSASS 비정상 접근·핸들 열기와 자격증명 덤프 도구 행위를 EDR 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- LSASS 보호(PPL)·자격증명 가드와 최소 권한·특권 분리를 적용(NIST AC-6·IA-5)</t>
+        </is>
+      </c>
       <c r="AN30" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -13236,10 +13682,15 @@
           <t>캐시된 도메인 자격증명 추출</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr"/>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Cached domain credentials</t>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>캐시된 도메인 자격증명 추출로 추가 계정 확보</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 오프라인에서 캐시된 도메인 자격증명을 깨 추가 계정을 확보할 수 있음
+- 메모리·레지스트리 기반이라 레거시가 보지 못하나 피해는 확산 단계에서 커짐</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -13249,7 +13700,7 @@
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
@@ -13304,7 +13755,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA31" s="14" t="inlineStr">
+      <c r="AA31" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -13334,7 +13785,7 @@
       <c r="AH31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI31" s="30" t="inlineStr">
+      <c r="AI31" s="29" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 일부</t>
         </is>
@@ -13347,7 +13798,14 @@
 AC-6 Least Privilege</t>
         </is>
       </c>
-      <c r="AM31" s="9" t="inlineStr"/>
+      <c r="AM31" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 캐시 자격증명 저장소 접근과 비정상 레지스트리·메모리 읽기를 EDR 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- 캐시 자격증명 수 제한·특권 분리와 강한 암호 정책을 적용(NIST AC-6·SI-4)</t>
+        </is>
+      </c>
       <c r="AN31" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -13375,10 +13833,15 @@
           <t>Kerberoasting·AS-REP 로스팅</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr"/>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Kerberoasting / AS-REP roasting</t>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>Kerberoasting·AS-REP 로스팅으로 도메인 권한 계정 탈취</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 Kerberos 요청으로 서비스 계정 티켓을 받아 오프라인에서 크랙해 도메인 권한 계정을 확보할 수 있음
+- 정상 인증 트래픽이라 레거시가 탐지하지 못하고 도메인 권한으로 직결됨</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -13388,7 +13851,7 @@
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
@@ -13447,7 +13910,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA32" s="12" t="inlineStr">
+      <c r="AA32" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -13477,7 +13940,7 @@
       <c r="AH32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI32" s="28" t="inlineStr">
+      <c r="AI32" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -13499,7 +13962,14 @@
 IA-5 Authenticator Management</t>
         </is>
       </c>
-      <c r="AM32" s="9" t="inlineStr"/>
+      <c r="AM32" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상적으로 많은 서비스 티켓 요청·약한 암호화 요청을 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- 서비스 계정에 길고 무작위한 암호·gMSA·강한 암호화를 적용하고 요청을 감사(NIST IA-5·AC-6)</t>
+        </is>
+      </c>
       <c r="AN32" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -13527,10 +13997,15 @@
           <t>입력 캡처·키로깅</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr"/>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Input capture / keylogging</t>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>입력 캡처·키로깅으로 자격증명 가로채기</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 키 입력·자격증명 입력을 가로채 추가 접근을 확보할 수 있음
+- 수집 속도·범위가 제한적이나 다른 단계를 잇는 수단이 됨</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -13540,7 +14015,7 @@
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
@@ -13595,7 +14070,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA33" s="14" t="inlineStr">
+      <c r="AA33" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -13625,7 +14100,7 @@
       <c r="AH33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI33" s="28" t="inlineStr">
+      <c r="AI33" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -13646,7 +14121,14 @@
 AC-6 Least Privilege</t>
         </is>
       </c>
-      <c r="AM33" s="9" t="inlineStr"/>
+      <c r="AM33" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 키보드 후킹·입력 가로채기 API와 비정상 입력 캡처를 EDR 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- 엔드포인트 행위 탐지·피싱 내성 MFA로 자격증명 탈취 가치를 낮춤(NIST SI-4·AC-6)</t>
+        </is>
+      </c>
       <c r="AN33" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -13674,10 +14156,15 @@
           <t>호스트·시스템·네트워크 구성 탐색</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr"/>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) System/host and network configuration discovery</t>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>정상 명령으로 호스트·시스템·네트워크 구성 탐색</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 명령으로 호스트·시스템·네트워크 구성을 파악해 확산·영향 계획의 토대를 만들 수 있음
+- 정상 질의라 레거시가 공백이나 단독 피해는 없음</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -13687,7 +14174,7 @@
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
@@ -13744,7 +14231,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA34" s="14" t="inlineStr">
+      <c r="AA34" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -13774,7 +14261,7 @@
       <c r="AH34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI34" s="28" t="inlineStr">
+      <c r="AI34" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -13795,7 +14282,14 @@
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM34" s="9" t="inlineStr"/>
+      <c r="AM34" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 짧은 시간의 연쇄 탐색 명령과 비정상 열거 패턴을 행위 기반으로 탐지(NIST SI-4·AU-6)
+■ 대응
+- 탐색 명령 사용을 기준선과 대조·감사하고 최소 기능을 적용(NIST SI-4·AU-6)</t>
+        </is>
+      </c>
       <c r="AN34" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -13823,10 +14317,15 @@
           <t>도메인·AD 열거(계정·신뢰·공유)</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr"/>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Domain/Active Directory enumeration</t>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>정상 LDAP·AD 질의로 공격 경로(관리자·신뢰·공유) 지도화</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 LDAP·AD 질의로 계정·신뢰·공유를 열거해 공격 경로를 지도화할 수 있음
+- 정상 트래픽이라 탐지가 어렵고 사람 운영 랜섬웨어의 핵심 정찰 단계임</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -13836,7 +14335,7 @@
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
@@ -13893,7 +14392,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA35" s="13" t="inlineStr">
+      <c r="AA35" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -13923,7 +14422,7 @@
       <c r="AH35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI35" s="28" t="inlineStr">
+      <c r="AI35" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -13946,7 +14445,14 @@
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM35" s="9" t="inlineStr"/>
+      <c r="AM35" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상 LDAP·AD 질의량과 공격 경로 지도화 도구 행위를 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- AD 질의·열거를 감사하고 공격 경로(관리자·신뢰)를 정리·최소화(NIST AC-6·AU-6)</t>
+        </is>
+      </c>
       <c r="AN35" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -13974,10 +14480,15 @@
           <t>보안 소프트웨어·방어 환경 탐색</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr"/>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Security software discovery</t>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>보안 소프트웨어·방어 환경 탐색으로 회피 준비</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 설치된 보안 제품을 확인해 회피·무력화를 준비할 수 있음
+- 사전 단계라 직접 피해는 없으나 이후 방어 회피로 이어짐</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -13987,7 +14498,7 @@
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
@@ -14042,7 +14553,7 @@
           <t>하</t>
         </is>
       </c>
-      <c r="AA36" s="15" t="inlineStr">
+      <c r="AA36" s="14" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
@@ -14072,7 +14583,7 @@
       <c r="AH36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI36" s="29" t="inlineStr">
+      <c r="AI36" s="28" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 다수</t>
         </is>
@@ -14084,7 +14595,14 @@
           <t>SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM36" s="9" t="inlineStr"/>
+      <c r="AM36" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 보안 제품·서비스 열거 명령과 비정상 조회를 행위 기반으로 탐지(NIST SI-4)
+■ 대응
+- 보안 제품 상태 변조 방지와 탐지 규칙·텔레메트리 중앙 감시를 적용(NIST SI-4)</t>
+        </is>
+      </c>
       <c r="AN36" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -14112,10 +14630,15 @@
           <t>원격 서비스 악용(RDP·SMB·WinRM)</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr"/>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Remote services (RDP/SMB/WinRM)</t>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>정상 원격 서비스(RDP·SMB·WinRM)로 자격증명 써 확산</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 RDP·SMB·WinRM 같은 정상 원격 관리 프로토콜로 탈취 자격증명을 써 호스트 간 확산할 수 있음
+- 정상 인증·세션이라 레거시가 악용과 구분하지 못하고 랜섬웨어 전개의 주 경로가 됨</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -14125,7 +14648,7 @@
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
@@ -14182,7 +14705,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA37" s="12" t="inlineStr">
+      <c r="AA37" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -14212,7 +14735,7 @@
       <c r="AH37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI37" s="28" t="inlineStr">
+      <c r="AI37" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -14234,7 +14757,15 @@
 SC-7 Boundary Protection</t>
         </is>
       </c>
-      <c r="AM37" s="9" t="inlineStr"/>
+      <c r="AM37" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상 원격 세션(출발지·시간·계정)과 내부 RDP·SMB 급증을 네트워크·아이덴티티 기반으로 탐지(NIST SI-4·SC-7)
+■ 대응
+- 내부 분할·관리 전용 경로·점프 호스트와 원격 서비스 접근 최소화를 적용(NIST AC-17·SC-7)
+- 참고: Mandiant 〈M-Trends〉</t>
+        </is>
+      </c>
       <c r="AN37" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉
@@ -14263,10 +14794,15 @@
           <t>대체 인증 자료 사용(Pass-the-Hash·Pass-the-Ticket)</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr"/>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Use alternate authentication material (PtH/PtT)</t>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>대체 인증 자료(PtH·PtT)로 평문 없이 인증해 확산</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 평문 암호 없이 해시·티켓으로 인증해 호스트 간 확산할 수 있음
+- 정상 인증으로 보여 레거시가 탐지하지 못하고 도메인 장악으로 직결됨</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -14276,7 +14812,7 @@
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
@@ -14336,7 +14872,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA38" s="12" t="inlineStr">
+      <c r="AA38" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -14366,7 +14902,7 @@
       <c r="AH38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI38" s="28" t="inlineStr">
+      <c r="AI38" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -14388,7 +14924,14 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM38" s="9" t="inlineStr"/>
+      <c r="AM38" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상 티켓·해시 사용과 로그온 유형·계정 불일치를 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- 특권 분리·로컬 관리자 암호 고유화(LAPS)·티켓 수명 축소와 재사용 탐지를 적용(NIST IA-2·AC-6)</t>
+        </is>
+      </c>
       <c r="AN38" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -14416,10 +14959,15 @@
           <t>측면 도구 전송</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr"/>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Lateral tool transfer</t>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>측면 도구 전송으로 내부 공유·세션 통해 도구 확산</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 내부 공유·세션으로 도구·페이로드를 호스트 간 퍼뜨릴 수 있음
+- 정상 채널·도구를 써 레거시가 구분하기 어려우나 피해는 실행·영향 단계에서 발생함</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -14429,7 +14977,7 @@
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
@@ -14484,7 +15032,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA39" s="14" t="inlineStr">
+      <c r="AA39" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -14514,7 +15062,7 @@
       <c r="AH39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI39" s="28" t="inlineStr">
+      <c r="AI39" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -14535,7 +15083,14 @@
 SC-7 Boundary Protection</t>
         </is>
       </c>
-      <c r="AM39" s="9" t="inlineStr"/>
+      <c r="AM39" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 내부 호스트 간 비정상 파일 전송·공유 쓰기를 네트워크·엔드포인트 기반으로 탐지(NIST SI-4·SC-7)
+■ 대응
+- 내부 분할·공유 권한 최소화와 측면 전송 모니터링을 적용(NIST SC-7·SI-4)</t>
+        </is>
+      </c>
       <c r="AN39" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -14563,10 +15118,15 @@
           <t>원격 서비스 취약점 악용(웜 확산)</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr"/>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exploitation of remote services (worm)</t>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>원격 서비스 취약점 악용으로 인증 없이 웜 확산</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 인증 없이 원격 서비스 취약점으로 패치되지 않은 호스트에 자동 확산(웜)할 수 있음
+- 패치 전 대규모 전파로 조직 전반이 빠르게 침해됨</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -14576,7 +15136,7 @@
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
@@ -14639,7 +15199,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA40" s="12" t="inlineStr">
+      <c r="AA40" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -14669,7 +15229,7 @@
       <c r="AH40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI40" s="28" t="inlineStr">
+      <c r="AI40" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -14691,7 +15251,15 @@
 SC-7 Boundary Protection</t>
         </is>
       </c>
-      <c r="AM40" s="9" t="inlineStr"/>
+      <c r="AM40" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 내부 취약 서비스 대상 악용 시도와 급격한 횡적 전파를 네트워크 기반으로 탐지(NIST SC-7·RA-5)
+■ 대응
+- 신속 패치·내부 분할과 취약 서비스 노출 최소화로 전파를 차단(NIST SI-2·RA-5·SC-7)
+- 참고: CISA 〈KEV Catalog〉</t>
+        </is>
+      </c>
       <c r="AN40" s="9" t="inlineStr">
         <is>
           <t>CISA 〈KEV Catalog〉
@@ -14720,10 +15288,15 @@
           <t>로컬·네트워크 공유 데이터 수집</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr"/>
-      <c r="F41" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Data from local system and network shares</t>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>로컬·네트워크 공유에서 반출 대상 데이터 수집</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 로컬·네트워크 공유에서 반출 대상 데이터를 모을 수 있음
+- 정상 접근으로 보여 레거시가 구분하기 어려우나 피해는 반출·영향 단계에서 실현됨</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -14733,7 +15306,7 @@
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
@@ -14789,7 +15362,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA41" s="14" t="inlineStr">
+      <c r="AA41" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -14819,7 +15392,7 @@
       <c r="AH41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI41" s="28" t="inlineStr">
+      <c r="AI41" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -14840,7 +15413,14 @@
 AC-6 Least Privilege</t>
         </is>
       </c>
-      <c r="AM41" s="9" t="inlineStr"/>
+      <c r="AM41" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 파일 열람·공유 접근과 비정상 수집 패턴을 행위 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- 데이터 접근 최소화·민감 데이터 분류와 접근 감사를 적용(NIST AC-6·SI-4)</t>
+        </is>
+      </c>
       <c r="AN41" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -14868,10 +15448,15 @@
           <t>수집 데이터 압축·암호화 스테이징</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr"/>
-      <c r="F42" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Archive/stage collected data</t>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>수집 데이터 압축·암호화 스테이징으로 내용 검사 회피</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 반출 전 데이터를 압축·암호화해 스테이징함으로써 내용 검사를 피할 수 있음
+- 암호화되어 레거시 DLP가 내용을 보지 못하나 단독 피해는 제한적임</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -14881,7 +15466,7 @@
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I42" s="9" t="inlineStr">
@@ -14937,7 +15522,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA42" s="14" t="inlineStr">
+      <c r="AA42" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -14967,7 +15552,7 @@
       <c r="AH42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI42" s="28" t="inlineStr">
+      <c r="AI42" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -14988,7 +15573,14 @@
 SC-7 Boundary Protection</t>
         </is>
       </c>
-      <c r="AM42" s="9" t="inlineStr"/>
+      <c r="AM42" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대용량 압축·암호화 산출물 생성과 스테이징 디렉터리 집중을 행위 기반으로 탐지(NIST SI-4·SC-7)
+■ 대응
+- 비정상 압축·스테이징 탐지와 반출 경로 통제를 병행(NIST SC-7·SI-4)</t>
+        </is>
+      </c>
       <c r="AN42" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -15016,10 +15608,15 @@
           <t>암호화 채널·비표준/정상 포트 위장 C2</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr"/>
-      <c r="F43" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Encrypted channel / non-standard or common port C2</t>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>암호화 채널·비표준/정상 포트 위장으로 C2 식별 회피</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 통제 트래픽을 암호화하고 정상·비표준 포트로 위장해 정상 트래픽에 섞을 수 있음
+- 레거시 IDS·방화벽이 내용을 보지 못해 C2 식별이 사실상 불가함</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -15029,7 +15626,7 @@
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr">
@@ -15085,7 +15682,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA43" s="13" t="inlineStr">
+      <c r="AA43" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -15115,7 +15712,7 @@
       <c r="AH43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI43" s="28" t="inlineStr">
+      <c r="AI43" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -15137,7 +15734,14 @@
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM43" s="9" t="inlineStr"/>
+      <c r="AM43" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- TLS 메타데이터·JA3/비컨 주기·목적지 평판을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
+■ 대응
+- egress 통제·TLS 가시성·목적지 평판 차단과 비컨 탐지를 적용(NIST SC-7·AU-6)</t>
+        </is>
+      </c>
       <c r="AN43" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -15165,10 +15769,15 @@
           <t>응용 계층 프로토콜(HTTPS) C2</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Application layer protocol (HTTPS) C2</t>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>응용 계층 프로토콜(HTTPS) C2로 포트·프로토콜 통제 통과</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 웹 트래픽처럼 보이는 HTTPS로 통제해 포트·프로토콜 기반 통제를 통과할 수 있음
+- 행위·네트워크 분석 없이는 정상 트래픽과 구분되지 않음</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -15178,7 +15787,7 @@
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I44" s="9" t="inlineStr">
@@ -15233,7 +15842,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA44" s="13" t="inlineStr">
+      <c r="AA44" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -15263,7 +15872,7 @@
       <c r="AH44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI44" s="28" t="inlineStr">
+      <c r="AI44" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -15285,7 +15894,14 @@
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM44" s="9" t="inlineStr"/>
+      <c r="AM44" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- HTTP(S) 비컨 주기·사용자 에이전트·목적지 이상을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
+■ 대응
+- 웹 프록시·egress 통제·목적지 평판과 비컨 탐지를 적용(NIST SC-7·AU-6)</t>
+        </is>
+      </c>
       <c r="AN44" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -15313,10 +15929,15 @@
           <t>정상 웹 서비스·클라우드 플랫폼 경유 C2</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr"/>
-      <c r="F45" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Web service / legitimate platform C2</t>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>정상 웹 서비스·클라우드 플랫폼을 C2 중계로 악용</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 GitHub·클라우드·협업 SaaS 같은 신뢰 도메인을 C2 중계로 악용할 수 있음
+- 차단하면 업무가 끊겨 레거시 차단·탐지가 어려움</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -15326,7 +15947,7 @@
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I45" s="9" t="inlineStr">
@@ -15389,7 +16010,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA45" s="13" t="inlineStr">
+      <c r="AA45" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -15419,7 +16040,7 @@
       <c r="AH45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI45" s="28" t="inlineStr">
+      <c r="AI45" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -15440,7 +16061,14 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM45" s="9" t="inlineStr"/>
+      <c r="AM45" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신뢰 SaaS로의 비정상 API 호출·데이터량·주기를 네트워크 기반으로 탐지(NIST SC-7·SI-4)
+■ 대응
+- 허용 SaaS·테넌트 제한과 egress 가시성·이상 사용 탐지를 적용(NIST SC-7·SI-4)</t>
+        </is>
+      </c>
       <c r="AN45" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -15468,10 +16096,15 @@
           <t>도메인 프런팅·다단계 프록시</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr"/>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Domain fronting / multi-hop proxy</t>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>도메인 프런팅·다단계 프록시로 도메인·IP 차단 우회</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 신뢰 CDN·프록시 뒤로 실제 C2를 숨겨 도메인·IP 기반 차단을 우회할 수 있음
+- 정상 도메인으로 보이나 TLS·주기 분석 등 탐지·차단 수단이 일부 존재함</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -15481,7 +16114,7 @@
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I46" s="9" t="inlineStr">
@@ -15537,7 +16170,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA46" s="14" t="inlineStr">
+      <c r="AA46" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -15567,7 +16200,7 @@
       <c r="AH46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI46" s="28" t="inlineStr">
+      <c r="AI46" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -15588,7 +16221,14 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM46" s="9" t="inlineStr"/>
+      <c r="AM46" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- SNI와 실제 목적지 불일치·비정상 CDN 사용을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
+■ 대응
+- TLS 검사·SNI 정책과 프록시 경유 egress 통제를 적용(NIST SC-7·SI-4)</t>
+        </is>
+      </c>
       <c r="AN46" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -15616,10 +16256,15 @@
           <t>인그레스 도구 전송(페이로드 반입)</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr"/>
-      <c r="F47" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Ingress tool transfer</t>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>정상 도구로 추가 페이로드 반입(인그레스 도구 전송)</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 certutil·curl 등 정상 도구로 추가 페이로드를 내려받아 반입할 수 있음
+- 정상 도구·암호화 채널을 써 레거시가 구분하기 어려우나 피해는 후속 단계에서 발생함</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -15629,7 +16274,7 @@
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I47" s="9" t="inlineStr">
@@ -15688,7 +16333,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA47" s="13" t="inlineStr">
+      <c r="AA47" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -15718,7 +16363,7 @@
       <c r="AH47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI47" s="28" t="inlineStr">
+      <c r="AI47" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -15740,7 +16385,15 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM47" s="9" t="inlineStr"/>
+      <c r="AM47" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 정상 다운로드 도구의 비정상 사용·외부 다운로드를 행위·네트워크 기반으로 탐지(NIST SI-4·SC-7)
+■ 대응
+- 불필요한 다운로드 도구 제한·egress 통제와 반입 파일 검사를 적용(NIST SI-3·SC-7)
+- 참고: LOLBAS 〈Project〉</t>
+        </is>
+      </c>
       <c r="AN47" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉
@@ -15769,10 +16422,15 @@
           <t>DNS 경유 C2·터널링</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr"/>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) DNS C2 / tunneling</t>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>DNS 경유 C2·터널링으로 방화벽 우회</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 거의 항상 허용되는 DNS 질의에 통제·데이터를 실어 방화벽을 우회할 수 있음
+- 레거시가 DNS 내용을 보지 않아 은닉 C2에 쓰이나 질의 이상 탐지로 일부 포착 가능함</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -15782,7 +16440,7 @@
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I48" s="9" t="inlineStr">
@@ -15837,7 +16495,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA48" s="14" t="inlineStr">
+      <c r="AA48" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -15867,7 +16525,7 @@
       <c r="AH48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI48" s="28" t="inlineStr">
+      <c r="AI48" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -15889,7 +16547,14 @@
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM48" s="9" t="inlineStr"/>
+      <c r="AM48" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상 DNS 질의량·엔트로피·긴 서브도메인을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
+■ 대응
+- DNS 로깅·필터링·내부 리졸버 강제와 이상 질의 차단을 적용(NIST SC-7·AU-6)</t>
+        </is>
+      </c>
       <c r="AN48" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -15917,10 +16582,15 @@
           <t>C2 채널 경유 반출</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr"/>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exfiltration over C2 channel</t>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>기존 암호화 C2 채널에 데이터 실어 반출</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 기존 암호화 C2 채널에 데이터를 실어 반출할 수 있음
+- 별도 채널이 없어 레거시 DLP가 탐지하기 어렵고 이중 협박 랜섬웨어의 유출 단계가 됨</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -15930,7 +16600,7 @@
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr">
@@ -15985,7 +16655,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA49" s="12" t="inlineStr">
+      <c r="AA49" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -16015,7 +16685,7 @@
       <c r="AH49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI49" s="28" t="inlineStr">
+      <c r="AI49" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -16037,7 +16707,14 @@
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AM49" s="9" t="inlineStr"/>
+      <c r="AM49" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- C2 세션의 비정상 업로드량·방향성과 비컨-대용량 전환을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
+■ 대응
+- egress 통제·데이터 유출 탐지와 C2 차단으로 반출을 막음(NIST SC-7·AU-6)</t>
+        </is>
+      </c>
       <c r="AN49" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -16065,10 +16742,15 @@
           <t>정상 웹 서비스·대체 프로토콜 경유 반출</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr"/>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exfiltration over web service / alternative protocol</t>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>정상 웹 서비스·대체 프로토콜로 대량 데이터 반출</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 클라우드 스토리지·정상 SaaS나 대체 프로토콜로 대량 데이터를 반출할 수 있음
+- 신뢰 도메인이라 차단·탐지가 어렵고 유출 규모가 큼</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -16078,7 +16760,7 @@
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I50" s="9" t="inlineStr">
@@ -16138,7 +16820,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA50" s="12" t="inlineStr">
+      <c r="AA50" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -16168,7 +16850,7 @@
       <c r="AH50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI50" s="28" t="inlineStr">
+      <c r="AI50" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -16189,7 +16871,14 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM50" s="9" t="inlineStr"/>
+      <c r="AM50" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신뢰 SaaS·외부 저장소로의 비정상 대량 업로드를 네트워크·DLP 기반으로 탐지(NIST SC-7·SI-4)
+■ 대응
+- 허용 SaaS 제한·egress 통제·DLP와 대용량 업로드 경보를 적용(NIST SC-7·SI-4)</t>
+        </is>
+      </c>
       <c r="AN50" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -16217,10 +16906,15 @@
           <t>데이터 암호화(사람 운영 랜섬웨어)</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr"/>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Data encrypted for impact (human-operated ransomware)</t>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>사람 운영 랜섬웨어의 도메인 장악 후 전사 암호화</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 도메인을 장악한 뒤 사람 운영 랜섬웨어로 전사 데이터를 암호화할 수 있음
+- 앞 단계가 레거시로 탐지되지 않아 암호화 시점에야 드러나 피해가 전면적임</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -16230,7 +16924,7 @@
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr">
@@ -16293,7 +16987,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA51" s="12" t="inlineStr">
+      <c r="AA51" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -16323,7 +17017,7 @@
       <c r="AH51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI51" s="28" t="inlineStr">
+      <c r="AI51" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -16345,7 +17039,15 @@
 CP-10 System Recovery and Reconstitution</t>
         </is>
       </c>
-      <c r="AM51" s="9" t="inlineStr"/>
+      <c r="AM51" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 파일 변경·암호화 행위와 선행 단계(자격증명·확산) 상관 이벤트를 행위 기반으로 탐지(NIST SI-4)
+■ 대응
+- 오프라인·불변 백업·복구 훈련과 선행 단계 조기 차단·분할을 적용(NIST CP-9·CP-10·SI-4)
+- 참고: Securelist 〈State of Ransomware 2026〉</t>
+        </is>
+      </c>
       <c r="AN51" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉
@@ -16374,10 +17076,15 @@
           <t>복구 방해(섀도 카피·백업 삭제)</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr"/>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Inhibit system recovery</t>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>섀도 카피·백업 삭제로 복구 방해</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 도구로 섀도 카피·백업을 지워 복구를 막을 수 있음
+- 랜섬웨어 피해를 돌이킬 수 없게 만드는 결정적 단계임</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -16387,7 +17094,7 @@
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I52" s="9" t="inlineStr">
@@ -16442,7 +17149,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA52" s="12" t="inlineStr">
+      <c r="AA52" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -16472,7 +17179,7 @@
       <c r="AH52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI52" s="28" t="inlineStr">
+      <c r="AI52" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -16494,7 +17201,14 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM52" s="9" t="inlineStr"/>
+      <c r="AM52" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 섀도 카피 삭제·백업 서비스 중지 명령을 행위 기반으로 탐지(NIST SI-4·CP-9)
+■ 대응
+- 오프라인·불변 백업과 백업 삭제 방지·권한 분리를 적용(NIST CP-9·SI-4)</t>
+        </is>
+      </c>
       <c r="AN52" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -16522,10 +17236,15 @@
           <t>데이터 파괴·와이퍼</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr"/>
-      <c r="F53" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Data destruction / wiper</t>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>데이터 파괴·와이퍼로 운영 중단·복구 불능</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 디스크·데이터를 파괴해 운영을 중단시킬 수 있음
+- 국가배후·핵티비스트의 파괴 작전으로 복구가 어렵고 피해가 전면적임</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -16535,7 +17254,7 @@
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr">
@@ -16595,7 +17314,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA53" s="13" t="inlineStr">
+      <c r="AA53" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -16625,7 +17344,7 @@
       <c r="AH53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI53" s="28" t="inlineStr">
+      <c r="AI53" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -16647,7 +17366,14 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AM53" s="9" t="inlineStr"/>
+      <c r="AM53" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 삭제·디스크 와이프·MBR 변조 행위를 행위 기반으로 탐지(NIST SI-4·SI-7)
+■ 대응
+- 오프라인·불변 백업과 무결성 보호·분할로 파괴 범위를 제한(NIST CP-9·SI-7)</t>
+        </is>
+      </c>
       <c r="AN53" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -16675,10 +17401,15 @@
           <t>서비스 중지·시스템 종료/재시작</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr"/>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Service stop / system shutdown</t>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>보안·백업·DB 서비스 중지·시스템 종료로 가용성 훼손</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 보안·백업·DB 서비스를 멈추거나 시스템을 종료해 암호화·파괴를 돕거나 가용성을 해칠 수 있음
+- 정상 관리 명령을 써 레거시가 구분하기 어려우나 단독 피해는 복구 가능함</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -16688,7 +17419,7 @@
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I54" s="9" t="inlineStr">
@@ -16744,7 +17475,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AA54" s="14" t="inlineStr">
+      <c r="AA54" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -16774,7 +17505,7 @@
       <c r="AH54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI54" s="28" t="inlineStr">
+      <c r="AI54" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -16795,7 +17526,14 @@
 CP-10 System Recovery and Reconstitution</t>
         </is>
       </c>
-      <c r="AM54" s="9" t="inlineStr"/>
+      <c r="AM54" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 보안·백업·DB 서비스의 비정상 중지와 대량 종료 명령을 행위 기반으로 탐지(NIST SI-4·CP-10)
+■ 대응
+- 중요 서비스 변조 방지·권한 분리와 신속 복구 체계를 적용(NIST CP-10·SI-4)</t>
+        </is>
+      </c>
       <c r="AN54" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -16823,10 +17561,15 @@
           <t>금전 탈취·이중 협박 갈취</t>
         </is>
       </c>
-      <c r="E55" s="9" t="inlineStr"/>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Financial theft / double-extortion</t>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>반출 데이터 공개 협박·부정 이체로 금전 피해 실현</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 반출 데이터 공개 협박이나 부정 이체로 금전 피해를 실현할 수 있음
+- 이중 협박은 백업 복구로도 막지 못해 대규모 금전·평판 피해로 직결됨</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
@@ -16836,7 +17579,7 @@
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="I55" s="9" t="inlineStr">
@@ -16899,7 +17642,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AA55" s="12" t="inlineStr">
+      <c r="AA55" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -16929,7 +17672,7 @@
       <c r="AH55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AI55" s="28" t="inlineStr">
+      <c r="AI55" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -16951,7 +17694,14 @@
 IR-4 Incident Handling</t>
         </is>
       </c>
-      <c r="AM55" s="9" t="inlineStr"/>
+      <c r="AM55" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 반출 선행 징후와 갈취·부정 이체 정황을 통합 모니터링(NIST SI-4·IR-4)
+■ 대응
+- 데이터 반출 차단·사고 대응·법집행 연계와 백업·복구를 병행(NIST IR-4·SI-4)</t>
+        </is>
+      </c>
       <c r="AN55" s="9" t="inlineStr">
         <is>
           <t>MITRE 〈ATT&amp;CK Enterprise v19.2〉</t>
@@ -17123,10 +17873,15 @@
           <t>인터넷 노출 경계·엣지 장비 취약점 악용(빠른 n-day·0-day)</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr"/>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exploitation of internet-facing edge/perimeter appliances</t>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>인터넷 노출 경계·엣지 장비 취약점으로 경계 안 직접 진입</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 VPN·방화벽·게이트웨이·파일전송 같은 인터넷 노출 엣지 장비의 공개 즉시 악용되는 취약점으로 경계 안으로 바로 들어올 수 있음
+- 엣지 장비는 EDR이 깔리지 않아 레거시 경계 통제로 탐지가 어렵고, KEV 등재가 매년 15~21%를 차지할 만큼 빠른 n-day·0-day가 집중됨</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -17154,7 +17909,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -17162,7 +17917,7 @@
       <c r="M3" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="N3" s="28" t="inlineStr">
+      <c r="N3" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -17178,7 +17933,17 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R3" s="9" t="inlineStr"/>
+      <c r="R3" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 외부 노출 자산을 지속 식별하고 엣지 장비의 취약점 공개·악용 동향을 신속 대조(NIST RA-5·SI-4)
+- 경계 장비의 비정상 설정 변경·세션·아웃바운드를 네트워크 기반으로 모니터링(NIST SC-7)
+■ 대응
+- 엣지 장비 신속 패치·가상 패치와 공개 취약점 노출 구간 최소화(NIST SI-2·RA-5)
+- 경계 장비를 분리·최소 노출하고 침해 전제의 세션 무효화·자격증명 교체 절차를 둠(NIST SC-7)
+- 참고: CISA 〈KEV Catalog〉 · CISA 〈Edge Device Advisory〉</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -17201,10 +17966,15 @@
           <t>외부 원격 서비스 악용(VPN·RDP·원격 관리)</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr"/>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exploitation/abuse of external remote services</t>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>탈취 계정·노출 원격 서비스로 정상 로그인처럼 경계 통과</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취한 계정이나 노출된 VPN·RDP·원격 관리로 정상 인증처럼 경계를 통과해 들어올 수 있음
+- 로그인 자체는 정상이라 레거시가 악용과 구분하지 못하고, 랜섬웨어 초기 침투의 주 경로가 됨</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
@@ -17232,7 +18002,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="L4" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -17240,7 +18010,7 @@
       <c r="M4" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="N4" s="28" t="inlineStr">
+      <c r="N4" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -17252,7 +18022,17 @@
         <v>43</v>
       </c>
       <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="9" t="inlineStr"/>
+      <c r="R4" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 원격 서비스 로그인의 비정상 위치·시간·장치와 MFA 미적용 경로를 아이덴티티·네트워크 기반으로 탐지(NIST SI-4·IA-2)
+- 노출 RDP·VPN·원격 관리 자산을 상시 식별(NIST SC-7)
+■ 대응
+- 모든 외부 원격 접근에 피싱 내성 MFA·조건부 접근을 적용하고 노출을 최소화(NIST AC-17·IA-2)
+- 원격 서비스 접근을 분리·제한하고 이상 로그인에 세션 차단(NIST SC-7)
+- 참고: Mandiant 〈M-Trends〉</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -17275,10 +18055,15 @@
           <t>드라이브바이 컴프로마이즈·워터링홀</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Drive-by compromise and watering hole</t>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>정상 사이트·광고망 경유 드라이브바이·워터링홀 감염</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 사이트·광고망을 침해하거나 워터링홀로 꾸며 방문자 단말을 감염시킬 수 있음
+- 경계에서 걸러지지 않는 정상 트래픽을 경유해 레거시 통제를 우회하나, 피해는 후속 실행·확산 단계에서 커짐</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -17306,7 +18091,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17314,7 +18099,7 @@
       <c r="M5" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="N5" s="29" t="inlineStr">
+      <c r="N5" s="28" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 다수</t>
         </is>
@@ -17326,7 +18111,14 @@
         <v>44</v>
       </c>
       <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="9" t="inlineStr"/>
+      <c r="R5" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 엔드포인트의 브라우저·플러그인 비정상 실행과 신뢰 사이트발 악성 리다이렉트를 행위 기반으로 탐지(NIST SI-3·SI-4)
+■ 대응
+- 브라우저·플러그인 신속 패치, 웹 격리·콘텐츠 필터링과 엔드포인트 행위 탐지를 적용(NIST SI-3·SC-7)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -17349,10 +18141,15 @@
           <t>이동식 매체·임시 접속 자산 경유 복제</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Replication through removable media</t>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>이동식 매체(USB)로 망분리·격리망 경계 우회 침투·전파</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 USB 등 이동식 매체로 망분리·격리망에 침투·전파해 네트워크 경계를 물리적으로 우회할 수 있음
+- 경계 통제 밖 경로라 레거시 네트워크 탐지가 보지 못하나 전파 속도·범위는 제한적임</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -17380,7 +18177,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L6" s="14" t="inlineStr">
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17388,7 +18185,7 @@
       <c r="M6" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="N6" s="28" t="inlineStr">
+      <c r="N6" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -17400,7 +18197,14 @@
         <v>28</v>
       </c>
       <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="9" t="inlineStr"/>
+      <c r="R6" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 이동식 매체 연결·자동 실행과 격리망 호스트의 비정상 실행을 엔드포인트 기반으로 탐지(NIST SI-3)
+■ 대응
+- 이동식 매체 사용을 통제·차단하고 자동 실행을 비활성화, 격리망 자산 반입 매체를 검사(NIST MP-7·SI-3)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -17423,10 +18227,15 @@
           <t>신뢰 관계(MSP·협력사·연동) 악용</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Trusted relationship abuse</t>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>MSP·협력사·연동 신뢰 경로 악용으로 다수 하위 고객 침해</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 MSP·원격 관리·연동 토큰 같은 신뢰 관계로 들어와 다수 하위 고객을 한 번에 침해할 수 있음
+- 정상 관리 트래픽을 경유해 레거시가 구분하지 못하고 피해가 연쇄됨</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -17454,7 +18263,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
+      <c r="L7" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -17462,7 +18271,7 @@
       <c r="M7" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="N7" s="28" t="inlineStr">
+      <c r="N7" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -17474,7 +18283,15 @@
         <v>13</v>
       </c>
       <c r="Q7" s="8" t="inlineStr"/>
-      <c r="R7" s="9" t="inlineStr"/>
+      <c r="R7" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신뢰 관계·연동 계정의 비정상 사용과 관리 도구발 대량·일괄 작업을 모니터링(NIST SI-4·AC-20)
+■ 대응
+- 공급·관리 관계에 최소 권한·분리·계약상 보안 요구를 적용하고 연동 토큰을 단기화·감사(NIST SR-3·CA-3·AC-20)
+- 참고: Mandiant 〈M-Trends〉</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -17497,10 +18314,15 @@
           <t>PowerShell 악용(파일리스 실행)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) PowerShell abuse (fileless execution)</t>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>PowerShell 파일리스 실행으로 시그니처 AV 무력화</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 PowerShell로 디스크에 파일을 남기지 않고 메모리에서 코드를 실행할 수 있음
+- 시그니처 AV가 보지 못해 행위 맥락으로만 탐지되며, 사람 운영 랜섬웨어·국가배후 작전의 기본 실행 수단임</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -17528,7 +18350,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="L8" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -17536,7 +18358,7 @@
       <c r="M8" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="28" t="inlineStr">
+      <c r="N8" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -17548,7 +18370,15 @@
         <v>233</v>
       </c>
       <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="9" t="inlineStr"/>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- PowerShell 스크립트 블록·명령줄 로깅과 비정상 실행 맥락(인코딩·다운로드·원격 실행)을 행위 기반으로 탐지(NIST SI-4·SI-3)
+■ 대응
+- 스크립트 로깅·제약 언어 모드·서명 정책과 최소 기능 원칙을 적용(NIST CM-7·SI-4)
+- 참고: LOLBAS 〈Project〉</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -17571,10 +18401,15 @@
           <t>Windows 관리 도구(WMI) 악용</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Windows Management Instrumentation abuse</t>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Windows 관리 도구(WMI) 악용으로 파일리스 실행·이동</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 WMI 같은 정상 관리 기능으로 파일 없이 실행·측면 이동·수집을 수행할 수 있음
+- 정상 관리 트래픽이라 레거시가 구분하지 못하나 단독 피해보다 다른 단계를 잇는 수단임</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -17602,7 +18437,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L9" s="14" t="inlineStr">
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17610,7 +18445,7 @@
       <c r="M9" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="N9" s="28" t="inlineStr">
+      <c r="N9" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -17622,7 +18457,14 @@
         <v>147</v>
       </c>
       <c r="Q9" s="8" t="inlineStr"/>
-      <c r="R9" s="9" t="inlineStr"/>
+      <c r="R9" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- WMI 이벤트 구독·원격 WMI 실행과 비정상 부모-자식 프로세스를 행위 기반으로 탐지(NIST SI-4·AU-6)
+■ 대응
+- WMI 원격 실행을 제한하고 관리 활동을 기준선과 대조·감사(NIST CM-7·AU-6)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -17645,10 +18487,15 @@
           <t>서명된 정상 바이너리 프록시 실행(LOLBin)</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Signed binary proxy execution (LOLBins)</t>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>서명된 정상 바이너리(LOLBin) 대리 실행으로 허용 목록 통과</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 OS에 서명·내장된 정상 바이너리로 악성 코드를 대리 실행하거나 페이로드를 내려받을 수 있음
+- 허용 목록·서명 검증을 통과해 레거시 통제가 구분하지 못함(LOLBAS 245개 수록)</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -17676,7 +18523,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -17684,7 +18531,7 @@
       <c r="M10" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="N10" s="28" t="inlineStr">
+      <c r="N10" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -17696,7 +18543,15 @@
         <v>2</v>
       </c>
       <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="9" t="inlineStr"/>
+      <c r="R10" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 정상 바이너리의 비정상 인자·부모 프로세스·네트워크 행위를 행위 기반으로 탐지(NIST SI-4·CM-7)
+■ 대응
+- 불필요한 LOLBin 실행을 허용 목록·애플리케이션 제어로 제한하고 무결성·실행 맥락을 감시(NIST CM-7·SI-7)
+- 참고: LOLBAS 〈Project〉</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -17719,10 +18574,15 @@
           <t>네이티브 API·시스템 서비스 실행</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Native API and system service execution</t>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>네이티브 API·시스템 서비스 직접 실행으로 후킹 탐지 회피</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 네이티브 API를 직접 호출하거나 시스템 서비스로 실행해 중간 도구를 거치지 않을 수 있음
+- 후킹 기반 탐지를 우회하나 피해는 후속 단계에서 발생함</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -17750,7 +18610,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L11" s="14" t="inlineStr">
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17758,7 +18618,7 @@
       <c r="M11" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="N11" s="29" t="inlineStr">
+      <c r="N11" s="28" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 다수</t>
         </is>
@@ -17770,7 +18630,14 @@
         <v>272</v>
       </c>
       <c r="Q11" s="8" t="inlineStr"/>
-      <c r="R11" s="9" t="inlineStr"/>
+      <c r="R11" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 커널 콜백·시스템 서비스 생성과 비정상 API 호출 시퀀스를 EDR 행위 기반으로 탐지(NIST SI-4)
+■ 대응
+- 커널 수준 가시성(EDR)과 최소 기능·서비스 생성 통제를 적용(NIST CM-7·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -17793,10 +18660,15 @@
           <t>윈도우 서비스 생성·수정</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Create or modify Windows service</t>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>윈도우 서비스 생성·수정으로 재부팅 후에도 접근 유지</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 서비스 등록 메커니즘으로 서비스를 만들거나 바꿔 지속·권한 상승에 쓸 수 있음
+- 정상 OS 기능이라 레거시가 악용과 구분하기 어려우나 단독 피해는 제한적임</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -17824,7 +18696,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L12" s="14" t="inlineStr">
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17832,7 +18704,7 @@
       <c r="M12" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="N12" s="28" t="inlineStr">
+      <c r="N12" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -17844,7 +18716,14 @@
         <v>140</v>
       </c>
       <c r="Q12" s="8" t="inlineStr"/>
-      <c r="R12" s="9" t="inlineStr"/>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규·수정 서비스와 비정상 바이너리 경로·시작 유형을 행위 기반으로 탐지(NIST SI-4·CM-7)
+■ 대응
+- 서비스 생성·변경을 감사·기준선과 대조하고 최소 권한을 적용(NIST CM-7·AU-6)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -17867,10 +18746,15 @@
           <t>부팅·로그온 자동 실행(레지스트리·시작 폴더)</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr"/>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Boot or logon autostart execution</t>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>부팅·로그온 자동 실행(레지스트리·시작 폴더) 지속성</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 레지스트리 런키·시작 폴더 등 자동 실행 지점에 등록해 재부팅·로그온 시 접근을 유지할 수 있음
+- 정상 자동 실행 메커니즘이라 레거시가 구분하기 어렵고 피해는 후속 단계에서 발생함</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -17898,7 +18782,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L13" s="14" t="inlineStr">
+      <c r="L13" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17906,7 +18790,7 @@
       <c r="M13" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="N13" s="28" t="inlineStr">
+      <c r="N13" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -17918,7 +18802,14 @@
         <v>6</v>
       </c>
       <c r="Q13" s="8" t="inlineStr"/>
-      <c r="R13" s="9" t="inlineStr"/>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자동 실행 지점(런키·시작 폴더·서비스)의 변경을 기준선과 대조해 탐지(NIST SI-4·SI-7)
+■ 대응
+- 자동 실행 지점 변경을 감사·무결성 검증하고 최소 기능을 적용(NIST CM-7·SI-7)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -17941,10 +18832,15 @@
           <t>예약 작업(스케줄드 태스크)</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr"/>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Scheduled task</t>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>예약 작업(스케줄드 태스크)으로 지속·주기 실행 확보</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 스케줄러로 예약 작업을 만들어 지속성과 주기 실행을 확보할 수 있음
+- 정상 기능이라 레거시가 구분하기 어려우나 단독 피해는 제한적임</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -17972,7 +18868,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L14" s="14" t="inlineStr">
+      <c r="L14" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17980,7 +18876,7 @@
       <c r="M14" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="N14" s="28" t="inlineStr">
+      <c r="N14" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -17992,7 +18888,14 @@
         <v>190</v>
       </c>
       <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="9" t="inlineStr"/>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규·수정 예약 작업과 비정상 트리거·실행 바이너리를 행위 기반으로 탐지(NIST SI-4·AU-6)
+■ 대응
+- 예약 작업 생성·변경을 감사하고 생성 권한을 최소화(NIST CM-7·AU-6)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -18015,10 +18918,15 @@
           <t>계정 조작·숨은 로컬 계정</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Account manipulation / hidden accounts</t>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>계정 조작·숨은 로컬 계정으로 신원 기반 지속 접근</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 계정·권한을 추가·변경하거나 숨은 로컬 계정을 만들어 지속 접근을 확보할 수 있음
+- 정상 계정 활동으로 보여 로그만으로는 악용을 구분하기 어려움</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -18046,7 +18954,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L15" s="14" t="inlineStr">
+      <c r="L15" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -18054,7 +18962,7 @@
       <c r="M15" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="N15" s="30" t="inlineStr">
+      <c r="N15" s="29" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 일부</t>
         </is>
@@ -18066,7 +18974,14 @@
         <v>9</v>
       </c>
       <c r="Q15" s="8" t="inlineStr"/>
-      <c r="R15" s="9" t="inlineStr"/>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규·변경 계정과 비정상 권한 부여·그룹 추가를 아이덴티티 기반으로 탐지(NIST AC-2·AU-6)
+■ 대응
+- 계정 생성·권한 변경을 승인·감사하고 휴면·불필요 계정을 정리(NIST AC-2·IA-4)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -18089,10 +19004,15 @@
           <t>프로세스 인젝션(인메모리 코드 주입)</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr"/>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Process injection</t>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>프로세스 인젝션(인메모리 코드 주입)으로 실행·은닉·상승</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 프로세스 메모리에 코드를 주입해 실행·은닉하고 권한을 높일 수 있음
+- 디스크 산출물이 없어 시그니처가 보지 못하며 거의 모든 고급 악성코드가 사용함</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -18120,7 +19040,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L16" s="13" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -18128,7 +19048,7 @@
       <c r="M16" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="N16" s="28" t="inlineStr">
+      <c r="N16" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18140,7 +19060,14 @@
         <v>87</v>
       </c>
       <c r="Q16" s="8" t="inlineStr"/>
-      <c r="R16" s="9" t="inlineStr"/>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 원격 스레드 생성·메모리 쓰기·비정상 메모리 영역 실행을 EDR 행위 기반으로 탐지(NIST SI-3·SI-4)
+■ 대응
+- 커널 수준 메모리 가시성(EDR)과 공격 표면 축소 규칙을 적용(NIST SI-3·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -18163,10 +19090,15 @@
           <t>접근 토큰 조작</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr"/>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Access token manipulation</t>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>접근 토큰 조작으로 다른 사용자 권한 사용</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 토큰을 복제·가장해 다른 사용자·서비스 권한으로 행동할 수 있음
+- 정상 인증 메커니즘을 써 레거시가 구분하기 어려우나 피해는 후속 단계에서 커짐</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -18194,7 +19126,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="L17" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -18202,7 +19134,7 @@
       <c r="M17" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="N17" s="28" t="inlineStr">
+      <c r="N17" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18214,7 +19146,14 @@
         <v>23</v>
       </c>
       <c r="Q17" s="8" t="inlineStr"/>
-      <c r="R17" s="9" t="inlineStr"/>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 토큰 복제·가장 API 호출과 비정상 권한 전환을 EDR 행위 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- 최소 권한·특권 계정 분리와 토큰 조작 탐지 규칙을 적용(NIST AC-6·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -18237,10 +19176,15 @@
           <t>사용자 계정 컨트롤(UAC) 우회</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr"/>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Bypass User Account Control</t>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>사용자 계정 컨트롤(UAC) 우회로 로컬 권한 상승</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 자동 상승 바이너리를 악용해 UAC를 우회하고 관리자 권한을 얻을 수 있음
+- 정상 메커니즘을 써 레거시가 구분하기 어려우나 단독 피해는 제한적임</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -18268,7 +19212,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L18" s="14" t="inlineStr">
+      <c r="L18" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -18276,7 +19220,7 @@
       <c r="M18" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="N18" s="28" t="inlineStr">
+      <c r="N18" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18288,7 +19232,14 @@
         <v>63</v>
       </c>
       <c r="Q18" s="8" t="inlineStr"/>
-      <c r="R18" s="9" t="inlineStr"/>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자동 상승 바이너리의 비정상 실행·레지스트리 조작을 행위 기반으로 탐지(NIST SI-4·CM-7)
+■ 대응
+- UAC 최고 수준 설정·관리자 승인 모드와 최소 권한을 적용(NIST AC-6·CM-7)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -18311,10 +19262,15 @@
           <t>권한 상승 취약점 악용(로컬·커널)</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr"/>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exploitation for privilege escalation</t>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>로컬·커널 취약점(또는 BYOVD)으로 SYSTEM·커널 권한 획득</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 로컬·커널 취약점이나 서명된 취약 드라이버(BYOVD)로 SYSTEM·커널 권한을 얻을 수 있음
+- 하위 계층이라 상위 보안 도구가 무력화되고 KEV 등재가 다수임</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -18342,7 +19298,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L19" s="13" t="inlineStr">
+      <c r="L19" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -18350,7 +19306,7 @@
       <c r="M19" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="N19" s="28" t="inlineStr">
+      <c r="N19" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18366,7 +19322,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R19" s="9" t="inlineStr"/>
+      <c r="R19" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 커널 드라이버 로드와 취약 드라이버 서명·해시를 차단 목록과 대조해 탐지(NIST SI-4)
+■ 대응
+- 취약 드라이버 차단 목록(HVCI·드라이버 블록리스트)과 신속 패치를 적용(NIST SI-2·SI-4)
+- 참고: LOLDrivers 〈Project〉</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -18389,10 +19353,15 @@
           <t>보안 도구 무력화(EDR 변조·BYOVD EDR 킬러)</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr"/>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Impair/disable security tools (EDR tampering, BYOVD killers)</t>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>서명된 취약 드라이버로 EDR·백신을 커널에서 무력화(BYOVD)</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 서명된 취약 드라이버를 올려 EDR·백신을 커널에서 무력화할 수 있음
+- 보안 도구 자체가 꺼지므로 이후 단계가 전부 가려지고, 여러 랜섬웨어·국가배후가 EDR 킬러를 공유함</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -18420,7 +19389,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L20" s="12" t="inlineStr">
+      <c r="L20" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -18428,7 +19397,7 @@
       <c r="M20" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="N20" s="28" t="inlineStr">
+      <c r="N20" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18440,7 +19409,15 @@
         <v>131</v>
       </c>
       <c r="Q20" s="8" t="inlineStr"/>
-      <c r="R20" s="9" t="inlineStr"/>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 보안 서비스 중지·드라이버 로드와 EDR 텔레메트리 단절을 행위·네트워크 기반으로 탐지(NIST SI-4·SI-7)
+■ 대응
+- 취약 드라이버 차단 목록(HVCI·블록리스트)·변조 방지와 보안 도구 상태를 중앙 감시(NIST SI-7·CM-7)
+- 참고: LOLDrivers 〈Project〉 · Hive Security 〈Modern Attack Techniques 2026〉</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -18463,10 +19440,15 @@
           <t>취약·악성 드라이버 로드(커널)</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr"/>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Load vulnerable/malicious kernel driver</t>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>취약·악성 드라이버 로드로 커널 은닉·무력화 토대 마련</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 취약·악성 드라이버를 커널에 올려 은닉·무력화의 토대를 만들 수 있음
+- 커널 계층이라 상위 보안 제품이 보지 못함</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -18494,7 +19476,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L21" s="12" t="inlineStr">
+      <c r="L21" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -18502,7 +19484,7 @@
       <c r="M21" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="N21" s="28" t="inlineStr">
+      <c r="N21" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18514,7 +19496,15 @@
         <v>4</v>
       </c>
       <c r="Q21" s="8" t="inlineStr"/>
-      <c r="R21" s="9" t="inlineStr"/>
+      <c r="R21" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신규 커널 드라이버 로드와 취약 드라이버 서명·해시를 차단 목록과 대조(NIST SI-7·SI-4)
+■ 대응
+- HVCI·드라이버 블록리스트로 취약 드라이버 로드를 차단(NIST SI-7·CM-7)
+- 참고: LOLDrivers 〈Project〉</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
@@ -18537,10 +19527,15 @@
           <t>지표 삭제(이벤트 로그·파일 삭제)</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Indicator removal (clear event logs, file deletion)</t>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>이벤트 로그·파일 삭제로 레거시 SIEM 탐지·분석 무력화</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 이벤트 로그·파일을 지워 레거시 SIEM 탐지와 사후 분석을 무력화할 수 있음
+- 원격·불변 로그가 없으면 흔적이 사라져 추적이 어려워짐</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -18568,7 +19563,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L22" s="13" t="inlineStr">
+      <c r="L22" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -18576,7 +19571,7 @@
       <c r="M22" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="N22" s="28" t="inlineStr">
+      <c r="N22" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18588,7 +19583,14 @@
         <v>335</v>
       </c>
       <c r="Q22" s="8" t="inlineStr"/>
-      <c r="R22" s="9" t="inlineStr"/>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 로그 삭제·감사 정책 변경 이벤트와 원격 수집 로그의 공백을 모니터링(NIST AU-6·SI-4)
+■ 대응
+- 원격·불변 로그 전송과 로그 삭제 방지·보존 정책을 적용(NIST AU-9·AU-6)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -18611,10 +19613,15 @@
           <t>위장(정상 이름·경로·서명 가장)</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Masquerading</t>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>정상 이름·경로·서명 가장(위장)으로 눈·규칙 탐지 회피</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 프로세스·경로·서명으로 위장해 사람 눈과 규칙 기반 탐지를 피할 수 있음
+- 정상처럼 보여 레거시가 구분하기 어려우나 단독 피해는 제한적임</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -18642,7 +19649,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L23" s="14" t="inlineStr">
+      <c r="L23" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -18650,7 +19657,7 @@
       <c r="M23" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="N23" s="28" t="inlineStr">
+      <c r="N23" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18662,7 +19669,14 @@
         <v>60</v>
       </c>
       <c r="Q23" s="8" t="inlineStr"/>
-      <c r="R23" s="9" t="inlineStr"/>
+      <c r="R23" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 정상 이름과 다른 경로·서명·해시 불일치를 무결성·행위 기반으로 탐지(NIST SI-4·SI-7)
+■ 대응
+- 바이너리 무결성·서명 검증과 정상 경로 기준선 대조를 적용(NIST SI-7·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -18685,10 +19699,15 @@
           <t>파일·정보 난독화·암호화</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr"/>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Obfuscated files or information</t>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>패킹·인코딩·암호화 난독화로 시그니처·정적 분석 회피</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 페이로드를 패킹·인코딩·암호화해 시그니처·정적 분석을 회피할 수 있음
+- 변종 양산으로 레거시 AV를 지속 우회하나 단독 피해는 제한적임</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -18716,7 +19735,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L24" s="14" t="inlineStr">
+      <c r="L24" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -18724,7 +19743,7 @@
       <c r="M24" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="N24" s="28" t="inlineStr">
+      <c r="N24" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18736,7 +19755,14 @@
         <v>160</v>
       </c>
       <c r="Q24" s="8" t="inlineStr"/>
-      <c r="R24" s="9" t="inlineStr"/>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 실행 시점 행위·언패킹과 비정상 인코딩·엔트로피를 행위 기반으로 탐지(NIST SI-3·SI-4)
+■ 대응
+- 시그니처 의존을 줄이고 행위 기반·샌드박스 분석을 병행(NIST SI-3·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -18759,10 +19785,15 @@
           <t>인메모리·반사 코드 로딩</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) In-memory / reflective code loading</t>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>인메모리·반사 코드 로딩으로 파일 기반 AV 원천 회피</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 디스크를 거치지 않고 메모리에서 페이로드를 로드·실행할 수 있음
+- 파일 기반 AV·시그니처가 원천적으로 보지 못해 행위·메모리 기반 탐지가 필요함</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
@@ -18790,7 +19821,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L25" s="13" t="inlineStr">
+      <c r="L25" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -18798,7 +19829,7 @@
       <c r="M25" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="N25" s="28" t="inlineStr">
+      <c r="N25" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18810,7 +19841,14 @@
         <v>32</v>
       </c>
       <c r="Q25" s="8" t="inlineStr"/>
-      <c r="R25" s="9" t="inlineStr"/>
+      <c r="R25" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 메모리 영역 할당·실행과 비정상 로딩을 EDR 메모리 스캔으로 탐지(NIST SI-3·SI-4)
+■ 대응
+- 메모리 가시성(EDR)·공격 표면 축소와 스크립트 실행 통제를 적용(NIST SI-3·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -18833,10 +19871,15 @@
           <t>루트킷(사용자·커널 은폐)</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr"/>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Rootkit</t>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>루트킷으로 프로세스·파일·연결을 하위 계층에서 은폐</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 루트킷으로 프로세스·파일·연결을 하위 계층에서 숨겨 탐지·분석을 방해할 수 있음
+- 레거시로는 존재 자체를 알기 어려워 장기 잠복에 쓰임</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -18864,7 +19907,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L26" s="13" t="inlineStr">
+      <c r="L26" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -18872,7 +19915,7 @@
       <c r="M26" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="N26" s="28" t="inlineStr">
+      <c r="N26" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18884,7 +19927,14 @@
         <v>32</v>
       </c>
       <c r="Q26" s="8" t="inlineStr"/>
-      <c r="R26" s="9" t="inlineStr"/>
+      <c r="R26" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 커널 무결성·드라이버 서명과 메모리·부트 무결성 검증으로 은폐를 탐지(NIST SI-7·SI-4)
+■ 대응
+- 커널 무결성 보호(HVCI)·보안 부팅과 하위 계층 텔레메트리를 확보(NIST SI-7·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -18907,10 +19957,15 @@
           <t>펌웨어·부트킷(UEFI) 지속·은닉</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr"/>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Pre-OS boot / firmware implant (bootkit)</t>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>펌웨어·부트킷(UEFI)으로 OS 아래 지속·은닉</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 OS 아래 펌웨어·부트 단계에 임플란트를 심어 재설치·디스크 교체에도 지속할 수 있음
+- OS 보안 제품의 가시성 밖이라 레거시·EDR 모두 사실상 공백임</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -18938,7 +19993,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L27" s="13" t="inlineStr">
+      <c r="L27" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -18946,7 +20001,7 @@
       <c r="M27" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="N27" s="31" t="inlineStr">
+      <c r="N27" s="30" t="inlineStr">
         <is>
           <t>이론·연구</t>
         </is>
@@ -18958,7 +20013,14 @@
         <v>0</v>
       </c>
       <c r="Q27" s="8" t="inlineStr"/>
-      <c r="R27" s="9" t="inlineStr"/>
+      <c r="R27" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 펌웨어·부트 무결성 측정(보안 부팅·측정 부팅)과 펌웨어 버전·해시 변화를 점검(NIST SI-7)
+■ 대응
+- 보안 부팅·펌웨어 무결성 검증·업데이트와 펌웨어 공급 신뢰를 관리(NIST SI-7·CM-7)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -18981,10 +20043,15 @@
           <t>OS 자격증명 덤프(LSASS 메모리)</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr"/>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) OS credential dumping (LSASS memory)</t>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>LSASS 메모리 덤프로 평문·해시 자격증명 탈취</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 LSASS 메모리에서 평문·해시 자격증명을 추출해 도메인 확산의 발판을 마련할 수 있음
+- 정상 프로세스 접근이라 레거시가 구분하지 못해 행위·EDR 기반 탐지가 필요함</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -19012,7 +20079,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L28" s="12" t="inlineStr">
+      <c r="L28" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -19020,7 +20087,7 @@
       <c r="M28" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="N28" s="28" t="inlineStr">
+      <c r="N28" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19032,7 +20099,14 @@
         <v>79</v>
       </c>
       <c r="Q28" s="8" t="inlineStr"/>
-      <c r="R28" s="9" t="inlineStr"/>
+      <c r="R28" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- LSASS 비정상 접근·핸들 열기와 자격증명 덤프 도구 행위를 EDR 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- LSASS 보호(PPL)·자격증명 가드와 최소 권한·특권 분리를 적용(NIST AC-6·IA-5)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -19055,10 +20129,15 @@
           <t>캐시된 도메인 자격증명 추출</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr"/>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Cached domain credentials</t>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>캐시된 도메인 자격증명 추출로 추가 계정 확보</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 오프라인에서 캐시된 도메인 자격증명을 깨 추가 계정을 확보할 수 있음
+- 메모리·레지스트리 기반이라 레거시가 보지 못하나 피해는 확산 단계에서 커짐</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -19086,7 +20165,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L29" s="14" t="inlineStr">
+      <c r="L29" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -19094,7 +20173,7 @@
       <c r="M29" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="N29" s="30" t="inlineStr">
+      <c r="N29" s="29" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 일부</t>
         </is>
@@ -19106,7 +20185,14 @@
         <v>8</v>
       </c>
       <c r="Q29" s="8" t="inlineStr"/>
-      <c r="R29" s="9" t="inlineStr"/>
+      <c r="R29" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 캐시 자격증명 저장소 접근과 비정상 레지스트리·메모리 읽기를 EDR 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- 캐시 자격증명 수 제한·특권 분리와 강한 암호 정책을 적용(NIST AC-6·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -19129,10 +20215,15 @@
           <t>Kerberoasting·AS-REP 로스팅</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr"/>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Kerberoasting / AS-REP roasting</t>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>Kerberoasting·AS-REP 로스팅으로 도메인 권한 계정 탈취</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 Kerberos 요청으로 서비스 계정 티켓을 받아 오프라인에서 크랙해 도메인 권한 계정을 확보할 수 있음
+- 정상 인증 트래픽이라 레거시가 탐지하지 못하고 도메인 권한으로 직결됨</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -19160,7 +20251,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L30" s="12" t="inlineStr">
+      <c r="L30" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -19168,7 +20259,7 @@
       <c r="M30" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="N30" s="28" t="inlineStr">
+      <c r="N30" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19180,7 +20271,14 @@
         <v>12</v>
       </c>
       <c r="Q30" s="8" t="inlineStr"/>
-      <c r="R30" s="9" t="inlineStr"/>
+      <c r="R30" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상적으로 많은 서비스 티켓 요청·약한 암호화 요청을 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- 서비스 계정에 길고 무작위한 암호·gMSA·강한 암호화를 적용하고 요청을 감사(NIST IA-5·AC-6)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
@@ -19203,10 +20301,15 @@
           <t>입력 캡처·키로깅</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr"/>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Input capture / keylogging</t>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>입력 캡처·키로깅으로 자격증명 가로채기</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 키 입력·자격증명 입력을 가로채 추가 접근을 확보할 수 있음
+- 수집 속도·범위가 제한적이나 다른 단계를 잇는 수단이 됨</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -19234,7 +20337,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L31" s="14" t="inlineStr">
+      <c r="L31" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -19242,7 +20345,7 @@
       <c r="M31" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="N31" s="28" t="inlineStr">
+      <c r="N31" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19254,7 +20357,14 @@
         <v>155</v>
       </c>
       <c r="Q31" s="8" t="inlineStr"/>
-      <c r="R31" s="9" t="inlineStr"/>
+      <c r="R31" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 키보드 후킹·입력 가로채기 API와 비정상 입력 캡처를 EDR 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- 엔드포인트 행위 탐지·피싱 내성 MFA로 자격증명 탈취 가치를 낮춤(NIST SI-4·AC-6)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
@@ -19277,10 +20387,15 @@
           <t>호스트·시스템·네트워크 구성 탐색</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr"/>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) System/host and network configuration discovery</t>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>정상 명령으로 호스트·시스템·네트워크 구성 탐색</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 명령으로 호스트·시스템·네트워크 구성을 파악해 확산·영향 계획의 토대를 만들 수 있음
+- 정상 질의라 레거시가 공백이나 단독 피해는 없음</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -19308,7 +20423,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L32" s="14" t="inlineStr">
+      <c r="L32" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -19316,7 +20431,7 @@
       <c r="M32" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="N32" s="28" t="inlineStr">
+      <c r="N32" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19328,7 +20443,14 @@
         <v>525</v>
       </c>
       <c r="Q32" s="8" t="inlineStr"/>
-      <c r="R32" s="9" t="inlineStr"/>
+      <c r="R32" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 짧은 시간의 연쇄 탐색 명령과 비정상 열거 패턴을 행위 기반으로 탐지(NIST SI-4·AU-6)
+■ 대응
+- 탐색 명령 사용을 기준선과 대조·감사하고 최소 기능을 적용(NIST SI-4·AU-6)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -19351,10 +20473,15 @@
           <t>도메인·AD 열거(계정·신뢰·공유)</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr"/>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Domain/Active Directory enumeration</t>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>정상 LDAP·AD 질의로 공격 경로(관리자·신뢰·공유) 지도화</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 LDAP·AD 질의로 계정·신뢰·공유를 열거해 공격 경로를 지도화할 수 있음
+- 정상 트래픽이라 탐지가 어렵고 사람 운영 랜섬웨어의 핵심 정찰 단계임</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -19382,7 +20509,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L33" s="13" t="inlineStr">
+      <c r="L33" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -19390,7 +20517,7 @@
       <c r="M33" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="N33" s="28" t="inlineStr">
+      <c r="N33" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19402,7 +20529,14 @@
         <v>135</v>
       </c>
       <c r="Q33" s="8" t="inlineStr"/>
-      <c r="R33" s="9" t="inlineStr"/>
+      <c r="R33" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상 LDAP·AD 질의량과 공격 경로 지도화 도구 행위를 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- AD 질의·열거를 감사하고 공격 경로(관리자·신뢰)를 정리·최소화(NIST AC-6·AU-6)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
@@ -19425,10 +20559,15 @@
           <t>보안 소프트웨어·방어 환경 탐색</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr"/>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Security software discovery</t>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>보안 소프트웨어·방어 환경 탐색으로 회피 준비</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 설치된 보안 제품을 확인해 회피·무력화를 준비할 수 있음
+- 사전 단계라 직접 피해는 없으나 이후 방어 회피로 이어짐</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -19456,7 +20595,7 @@
           <t>하</t>
         </is>
       </c>
-      <c r="L34" s="15" t="inlineStr">
+      <c r="L34" s="14" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
@@ -19464,7 +20603,7 @@
       <c r="M34" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="N34" s="29" t="inlineStr">
+      <c r="N34" s="28" t="inlineStr">
         <is>
           <t>ATT&amp;CK 사례·KEV 다수</t>
         </is>
@@ -19476,7 +20615,14 @@
         <v>141</v>
       </c>
       <c r="Q34" s="8" t="inlineStr"/>
-      <c r="R34" s="9" t="inlineStr"/>
+      <c r="R34" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 보안 제품·서비스 열거 명령과 비정상 조회를 행위 기반으로 탐지(NIST SI-4)
+■ 대응
+- 보안 제품 상태 변조 방지와 탐지 규칙·텔레메트리 중앙 감시를 적용(NIST SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
@@ -19499,10 +20645,15 @@
           <t>원격 서비스 악용(RDP·SMB·WinRM)</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr"/>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Remote services (RDP/SMB/WinRM)</t>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>정상 원격 서비스(RDP·SMB·WinRM)로 자격증명 써 확산</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 RDP·SMB·WinRM 같은 정상 원격 관리 프로토콜로 탈취 자격증명을 써 호스트 간 확산할 수 있음
+- 정상 인증·세션이라 레거시가 악용과 구분하지 못하고 랜섬웨어 전개의 주 경로가 됨</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -19530,7 +20681,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L35" s="12" t="inlineStr">
+      <c r="L35" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -19538,7 +20689,7 @@
       <c r="M35" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="28" t="inlineStr">
+      <c r="N35" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19550,7 +20701,15 @@
         <v>111</v>
       </c>
       <c r="Q35" s="8" t="inlineStr"/>
-      <c r="R35" s="9" t="inlineStr"/>
+      <c r="R35" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상 원격 세션(출발지·시간·계정)과 내부 RDP·SMB 급증을 네트워크·아이덴티티 기반으로 탐지(NIST SI-4·SC-7)
+■ 대응
+- 내부 분할·관리 전용 경로·점프 호스트와 원격 서비스 접근 최소화를 적용(NIST AC-17·SC-7)
+- 참고: Mandiant 〈M-Trends〉</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
@@ -19573,10 +20732,15 @@
           <t>대체 인증 자료 사용(Pass-the-Hash·Pass-the-Ticket)</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr"/>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Use alternate authentication material (PtH/PtT)</t>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>대체 인증 자료(PtH·PtT)로 평문 없이 인증해 확산</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 평문 암호 없이 해시·티켓으로 인증해 호스트 간 확산할 수 있음
+- 정상 인증으로 보여 레거시가 탐지하지 못하고 도메인 장악으로 직결됨</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -19604,7 +20768,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L36" s="12" t="inlineStr">
+      <c r="L36" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -19612,7 +20776,7 @@
       <c r="M36" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N36" s="28" t="inlineStr">
+      <c r="N36" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19624,7 +20788,14 @@
         <v>26</v>
       </c>
       <c r="Q36" s="8" t="inlineStr"/>
-      <c r="R36" s="9" t="inlineStr"/>
+      <c r="R36" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상 티켓·해시 사용과 로그온 유형·계정 불일치를 아이덴티티 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- 특권 분리·로컬 관리자 암호 고유화(LAPS)·티켓 수명 축소와 재사용 탐지를 적용(NIST IA-2·AC-6)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
@@ -19647,10 +20818,15 @@
           <t>측면 도구 전송</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr"/>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Lateral tool transfer</t>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>측면 도구 전송으로 내부 공유·세션 통해 도구 확산</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 내부 공유·세션으로 도구·페이로드를 호스트 간 퍼뜨릴 수 있음
+- 정상 채널·도구를 써 레거시가 구분하기 어려우나 피해는 실행·영향 단계에서 발생함</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -19678,7 +20854,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L37" s="14" t="inlineStr">
+      <c r="L37" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -19686,7 +20862,7 @@
       <c r="M37" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="N37" s="28" t="inlineStr">
+      <c r="N37" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19698,7 +20874,14 @@
         <v>55</v>
       </c>
       <c r="Q37" s="8" t="inlineStr"/>
-      <c r="R37" s="9" t="inlineStr"/>
+      <c r="R37" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 내부 호스트 간 비정상 파일 전송·공유 쓰기를 네트워크·엔드포인트 기반으로 탐지(NIST SI-4·SC-7)
+■ 대응
+- 내부 분할·공유 권한 최소화와 측면 전송 모니터링을 적용(NIST SC-7·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
@@ -19721,10 +20904,15 @@
           <t>원격 서비스 취약점 악용(웜 확산)</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr"/>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exploitation of remote services (worm)</t>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>원격 서비스 취약점 악용으로 인증 없이 웜 확산</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 인증 없이 원격 서비스 취약점으로 패치되지 않은 호스트에 자동 확산(웜)할 수 있음
+- 패치 전 대규모 전파로 조직 전반이 빠르게 침해됨</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -19752,7 +20940,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L38" s="12" t="inlineStr">
+      <c r="L38" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -19760,7 +20948,7 @@
       <c r="M38" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="N38" s="28" t="inlineStr">
+      <c r="N38" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19776,7 +20964,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="R38" s="9" t="inlineStr"/>
+      <c r="R38" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 내부 취약 서비스 대상 악용 시도와 급격한 횡적 전파를 네트워크 기반으로 탐지(NIST SC-7·RA-5)
+■ 대응
+- 신속 패치·내부 분할과 취약 서비스 노출 최소화로 전파를 차단(NIST SI-2·RA-5·SC-7)
+- 참고: CISA 〈KEV Catalog〉</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
@@ -19799,10 +20995,15 @@
           <t>로컬·네트워크 공유 데이터 수집</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr"/>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Data from local system and network shares</t>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>로컬·네트워크 공유에서 반출 대상 데이터 수집</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 로컬·네트워크 공유에서 반출 대상 데이터를 모을 수 있음
+- 정상 접근으로 보여 레거시가 구분하기 어려우나 피해는 반출·영향 단계에서 실현됨</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -19830,7 +21031,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L39" s="14" t="inlineStr">
+      <c r="L39" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -19838,7 +21039,7 @@
       <c r="M39" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="N39" s="28" t="inlineStr">
+      <c r="N39" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19850,7 +21051,14 @@
         <v>233</v>
       </c>
       <c r="Q39" s="8" t="inlineStr"/>
-      <c r="R39" s="9" t="inlineStr"/>
+      <c r="R39" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 파일 열람·공유 접근과 비정상 수집 패턴을 행위 기반으로 탐지(NIST SI-4·AC-6)
+■ 대응
+- 데이터 접근 최소화·민감 데이터 분류와 접근 감사를 적용(NIST AC-6·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
@@ -19873,10 +21081,15 @@
           <t>수집 데이터 압축·암호화 스테이징</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr"/>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Archive/stage collected data</t>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>수집 데이터 압축·암호화 스테이징으로 내용 검사 회피</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 반출 전 데이터를 압축·암호화해 스테이징함으로써 내용 검사를 피할 수 있음
+- 암호화되어 레거시 DLP가 내용을 보지 못하나 단독 피해는 제한적임</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -19904,7 +21117,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L40" s="14" t="inlineStr">
+      <c r="L40" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -19912,7 +21125,7 @@
       <c r="M40" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="N40" s="28" t="inlineStr">
+      <c r="N40" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19924,7 +21137,14 @@
         <v>66</v>
       </c>
       <c r="Q40" s="8" t="inlineStr"/>
-      <c r="R40" s="9" t="inlineStr"/>
+      <c r="R40" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대용량 압축·암호화 산출물 생성과 스테이징 디렉터리 집중을 행위 기반으로 탐지(NIST SI-4·SC-7)
+■ 대응
+- 비정상 압축·스테이징 탐지와 반출 경로 통제를 병행(NIST SC-7·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
@@ -19947,10 +21167,15 @@
           <t>암호화 채널·비표준/정상 포트 위장 C2</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr"/>
-      <c r="F41" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Encrypted channel / non-standard or common port C2</t>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>암호화 채널·비표준/정상 포트 위장으로 C2 식별 회피</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 통제 트래픽을 암호화하고 정상·비표준 포트로 위장해 정상 트래픽에 섞을 수 있음
+- 레거시 IDS·방화벽이 내용을 보지 못해 C2 식별이 사실상 불가함</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -19978,7 +21203,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L41" s="13" t="inlineStr">
+      <c r="L41" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -19986,7 +21211,7 @@
       <c r="M41" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="N41" s="28" t="inlineStr">
+      <c r="N41" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19998,7 +21223,14 @@
         <v>79</v>
       </c>
       <c r="Q41" s="8" t="inlineStr"/>
-      <c r="R41" s="9" t="inlineStr"/>
+      <c r="R41" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- TLS 메타데이터·JA3/비컨 주기·목적지 평판을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
+■ 대응
+- egress 통제·TLS 가시성·목적지 평판 차단과 비컨 탐지를 적용(NIST SC-7·AU-6)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
@@ -20021,10 +21253,15 @@
           <t>응용 계층 프로토콜(HTTPS) C2</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr"/>
-      <c r="F42" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Application layer protocol (HTTPS) C2</t>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>응용 계층 프로토콜(HTTPS) C2로 포트·프로토콜 통제 통과</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 웹 트래픽처럼 보이는 HTTPS로 통제해 포트·프로토콜 기반 통제를 통과할 수 있음
+- 행위·네트워크 분석 없이는 정상 트래픽과 구분되지 않음</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -20052,7 +21289,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L42" s="13" t="inlineStr">
+      <c r="L42" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -20060,7 +21297,7 @@
       <c r="M42" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="N42" s="28" t="inlineStr">
+      <c r="N42" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -20072,7 +21309,14 @@
         <v>422</v>
       </c>
       <c r="Q42" s="8" t="inlineStr"/>
-      <c r="R42" s="9" t="inlineStr"/>
+      <c r="R42" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- HTTP(S) 비컨 주기·사용자 에이전트·목적지 이상을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
+■ 대응
+- 웹 프록시·egress 통제·목적지 평판과 비컨 탐지를 적용(NIST SC-7·AU-6)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
@@ -20095,10 +21339,15 @@
           <t>정상 웹 서비스·클라우드 플랫폼 경유 C2</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr"/>
-      <c r="F43" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Web service / legitimate platform C2</t>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>정상 웹 서비스·클라우드 플랫폼을 C2 중계로 악용</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 GitHub·클라우드·협업 SaaS 같은 신뢰 도메인을 C2 중계로 악용할 수 있음
+- 차단하면 업무가 끊겨 레거시 차단·탐지가 어려움</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -20126,7 +21375,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L43" s="13" t="inlineStr">
+      <c r="L43" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -20134,7 +21383,7 @@
       <c r="M43" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="N43" s="28" t="inlineStr">
+      <c r="N43" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -20146,7 +21395,14 @@
         <v>50</v>
       </c>
       <c r="Q43" s="8" t="inlineStr"/>
-      <c r="R43" s="9" t="inlineStr"/>
+      <c r="R43" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신뢰 SaaS로의 비정상 API 호출·데이터량·주기를 네트워크 기반으로 탐지(NIST SC-7·SI-4)
+■ 대응
+- 허용 SaaS·테넌트 제한과 egress 가시성·이상 사용 탐지를 적용(NIST SC-7·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
@@ -20169,10 +21425,15 @@
           <t>도메인 프런팅·다단계 프록시</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Domain fronting / multi-hop proxy</t>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>도메인 프런팅·다단계 프록시로 도메인·IP 차단 우회</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 신뢰 CDN·프록시 뒤로 실제 C2를 숨겨 도메인·IP 기반 차단을 우회할 수 있음
+- 정상 도메인으로 보이나 TLS·주기 분석 등 탐지·차단 수단이 일부 존재함</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -20200,7 +21461,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L44" s="14" t="inlineStr">
+      <c r="L44" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -20208,7 +21469,7 @@
       <c r="M44" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="N44" s="28" t="inlineStr">
+      <c r="N44" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -20220,7 +21481,14 @@
         <v>81</v>
       </c>
       <c r="Q44" s="8" t="inlineStr"/>
-      <c r="R44" s="9" t="inlineStr"/>
+      <c r="R44" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- SNI와 실제 목적지 불일치·비정상 CDN 사용을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
+■ 대응
+- TLS 검사·SNI 정책과 프록시 경유 egress 통제를 적용(NIST SC-7·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
@@ -20243,10 +21511,15 @@
           <t>인그레스 도구 전송(페이로드 반입)</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr"/>
-      <c r="F45" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Ingress tool transfer</t>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>정상 도구로 추가 페이로드 반입(인그레스 도구 전송)</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 certutil·curl 등 정상 도구로 추가 페이로드를 내려받아 반입할 수 있음
+- 정상 도구·암호화 채널을 써 레거시가 구분하기 어려우나 피해는 후속 단계에서 발생함</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -20274,7 +21547,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L45" s="13" t="inlineStr">
+      <c r="L45" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -20282,7 +21555,7 @@
       <c r="M45" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="N45" s="28" t="inlineStr">
+      <c r="N45" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -20294,7 +21567,15 @@
         <v>520</v>
       </c>
       <c r="Q45" s="8" t="inlineStr"/>
-      <c r="R45" s="9" t="inlineStr"/>
+      <c r="R45" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 정상 다운로드 도구의 비정상 사용·외부 다운로드를 행위·네트워크 기반으로 탐지(NIST SI-4·SC-7)
+■ 대응
+- 불필요한 다운로드 도구 제한·egress 통제와 반입 파일 검사를 적용(NIST SI-3·SC-7)
+- 참고: LOLBAS 〈Project〉</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
@@ -20317,10 +21598,15 @@
           <t>DNS 경유 C2·터널링</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr"/>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) DNS C2 / tunneling</t>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>DNS 경유 C2·터널링으로 방화벽 우회</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 거의 항상 허용되는 DNS 질의에 통제·데이터를 실어 방화벽을 우회할 수 있음
+- 레거시가 DNS 내용을 보지 않아 은닉 C2에 쓰이나 질의 이상 탐지로 일부 포착 가능함</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -20348,7 +21634,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L46" s="14" t="inlineStr">
+      <c r="L46" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -20356,7 +21642,7 @@
       <c r="M46" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="N46" s="28" t="inlineStr">
+      <c r="N46" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -20368,7 +21654,14 @@
         <v>55</v>
       </c>
       <c r="Q46" s="8" t="inlineStr"/>
-      <c r="R46" s="9" t="inlineStr"/>
+      <c r="R46" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 비정상 DNS 질의량·엔트로피·긴 서브도메인을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
+■ 대응
+- DNS 로깅·필터링·내부 리졸버 강제와 이상 질의 차단을 적용(NIST SC-7·AU-6)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
@@ -20391,10 +21684,15 @@
           <t>C2 채널 경유 반출</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr"/>
-      <c r="F47" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exfiltration over C2 channel</t>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>기존 암호화 C2 채널에 데이터 실어 반출</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 기존 암호화 C2 채널에 데이터를 실어 반출할 수 있음
+- 별도 채널이 없어 레거시 DLP가 탐지하기 어렵고 이중 협박 랜섬웨어의 유출 단계가 됨</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -20422,7 +21720,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L47" s="12" t="inlineStr">
+      <c r="L47" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -20430,7 +21728,7 @@
       <c r="M47" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="N47" s="28" t="inlineStr">
+      <c r="N47" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -20442,7 +21740,14 @@
         <v>203</v>
       </c>
       <c r="Q47" s="8" t="inlineStr"/>
-      <c r="R47" s="9" t="inlineStr"/>
+      <c r="R47" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- C2 세션의 비정상 업로드량·방향성과 비컨-대용량 전환을 네트워크 기반으로 탐지(NIST SC-7·SI-4)
+■ 대응
+- egress 통제·데이터 유출 탐지와 C2 차단으로 반출을 막음(NIST SC-7·AU-6)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
@@ -20465,10 +21770,15 @@
           <t>정상 웹 서비스·대체 프로토콜 경유 반출</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr"/>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Exfiltration over web service / alternative protocol</t>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>정상 웹 서비스·대체 프로토콜로 대량 데이터 반출</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 클라우드 스토리지·정상 SaaS나 대체 프로토콜로 대량 데이터를 반출할 수 있음
+- 신뢰 도메인이라 차단·탐지가 어렵고 유출 규모가 큼</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -20496,7 +21806,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L48" s="12" t="inlineStr">
+      <c r="L48" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -20504,7 +21814,7 @@
       <c r="M48" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="N48" s="28" t="inlineStr">
+      <c r="N48" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -20516,7 +21826,14 @@
         <v>25</v>
       </c>
       <c r="Q48" s="8" t="inlineStr"/>
-      <c r="R48" s="9" t="inlineStr"/>
+      <c r="R48" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 신뢰 SaaS·외부 저장소로의 비정상 대량 업로드를 네트워크·DLP 기반으로 탐지(NIST SC-7·SI-4)
+■ 대응
+- 허용 SaaS 제한·egress 통제·DLP와 대용량 업로드 경보를 적용(NIST SC-7·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
@@ -20539,10 +21856,15 @@
           <t>데이터 암호화(사람 운영 랜섬웨어)</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr"/>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Data encrypted for impact (human-operated ransomware)</t>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>사람 운영 랜섬웨어의 도메인 장악 후 전사 암호화</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 도메인을 장악한 뒤 사람 운영 랜섬웨어로 전사 데이터를 암호화할 수 있음
+- 앞 단계가 레거시로 탐지되지 않아 암호화 시점에야 드러나 피해가 전면적임</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -20570,7 +21892,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L49" s="12" t="inlineStr">
+      <c r="L49" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -20578,7 +21900,7 @@
       <c r="M49" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="N49" s="28" t="inlineStr">
+      <c r="N49" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -20590,7 +21912,15 @@
         <v>85</v>
       </c>
       <c r="Q49" s="8" t="inlineStr"/>
-      <c r="R49" s="9" t="inlineStr"/>
+      <c r="R49" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 파일 변경·암호화 행위와 선행 단계(자격증명·확산) 상관 이벤트를 행위 기반으로 탐지(NIST SI-4)
+■ 대응
+- 오프라인·불변 백업·복구 훈련과 선행 단계 조기 차단·분할을 적용(NIST CP-9·CP-10·SI-4)
+- 참고: Securelist 〈State of Ransomware 2026〉</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
@@ -20613,10 +21943,15 @@
           <t>복구 방해(섀도 카피·백업 삭제)</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr"/>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Inhibit system recovery</t>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>섀도 카피·백업 삭제로 복구 방해</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 도구로 섀도 카피·백업을 지워 복구를 막을 수 있음
+- 랜섬웨어 피해를 돌이킬 수 없게 만드는 결정적 단계임</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -20644,7 +21979,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L50" s="12" t="inlineStr">
+      <c r="L50" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -20652,7 +21987,7 @@
       <c r="M50" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="N50" s="28" t="inlineStr">
+      <c r="N50" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -20664,7 +21999,14 @@
         <v>56</v>
       </c>
       <c r="Q50" s="8" t="inlineStr"/>
-      <c r="R50" s="9" t="inlineStr"/>
+      <c r="R50" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 섀도 카피 삭제·백업 서비스 중지 명령을 행위 기반으로 탐지(NIST SI-4·CP-9)
+■ 대응
+- 오프라인·불변 백업과 백업 삭제 방지·권한 분리를 적용(NIST CP-9·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
@@ -20687,10 +22029,15 @@
           <t>데이터 파괴·와이퍼</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr"/>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Data destruction / wiper</t>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>데이터 파괴·와이퍼로 운영 중단·복구 불능</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 디스크·데이터를 파괴해 운영을 중단시킬 수 있음
+- 국가배후·핵티비스트의 파괴 작전으로 복구가 어렵고 피해가 전면적임</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -20718,7 +22065,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L51" s="13" t="inlineStr">
+      <c r="L51" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -20726,7 +22073,7 @@
       <c r="M51" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="N51" s="28" t="inlineStr">
+      <c r="N51" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -20738,7 +22085,14 @@
         <v>40</v>
       </c>
       <c r="Q51" s="8" t="inlineStr"/>
-      <c r="R51" s="9" t="inlineStr"/>
+      <c r="R51" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 삭제·디스크 와이프·MBR 변조 행위를 행위 기반으로 탐지(NIST SI-4·SI-7)
+■ 대응
+- 오프라인·불변 백업과 무결성 보호·분할로 파괴 범위를 제한(NIST CP-9·SI-7)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
@@ -20761,10 +22115,15 @@
           <t>서비스 중지·시스템 종료/재시작</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr"/>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Service stop / system shutdown</t>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>보안·백업·DB 서비스 중지·시스템 종료로 가용성 훼손</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 보안·백업·DB 서비스를 멈추거나 시스템을 종료해 암호화·파괴를 돕거나 가용성을 해칠 수 있음
+- 정상 관리 명령을 써 레거시가 구분하기 어려우나 단독 피해는 복구 가능함</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -20792,7 +22151,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="L52" s="14" t="inlineStr">
+      <c r="L52" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -20800,7 +22159,7 @@
       <c r="M52" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="N52" s="28" t="inlineStr">
+      <c r="N52" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -20812,7 +22171,14 @@
         <v>76</v>
       </c>
       <c r="Q52" s="8" t="inlineStr"/>
-      <c r="R52" s="9" t="inlineStr"/>
+      <c r="R52" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 보안·백업·DB 서비스의 비정상 중지와 대량 종료 명령을 행위 기반으로 탐지(NIST SI-4·CP-10)
+■ 대응
+- 중요 서비스 변조 방지·권한 분리와 신속 복구 체계를 적용(NIST CP-10·SI-4)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
@@ -20835,10 +22201,15 @@
           <t>금전 탈취·이중 협박 갈취</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr"/>
-      <c r="F53" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Financial theft / double-extortion</t>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>반출 데이터 공개 협박·부정 이체로 금전 피해 실현</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 반출 데이터 공개 협박이나 부정 이체로 금전 피해를 실현할 수 있음
+- 이중 협박은 백업 복구로도 막지 못해 대규모 금전·평판 피해로 직결됨</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -20866,7 +22237,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="L53" s="12" t="inlineStr">
+      <c r="L53" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -20874,7 +22245,7 @@
       <c r="M53" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="N53" s="28" t="inlineStr">
+      <c r="N53" s="27" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -20886,7 +22257,14 @@
         <v>26</v>
       </c>
       <c r="Q53" s="8" t="inlineStr"/>
-      <c r="R53" s="9" t="inlineStr"/>
+      <c r="R53" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 반출 선행 징후와 갈취·부정 이체 정황을 통합 모니터링(NIST SI-4·IR-4)
+■ 대응
+- 데이터 반출 차단·사고 대응·법집행 연계와 백업·복구를 병행(NIST IR-4·SI-4)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:R53"/>
@@ -22032,16 +23410,757 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>공격 체인 시나리오 — ③단계(data/scenarios.yaml)에서 작성</t>
+          <t>공격 체인 시나리오 8개 — 실제 사고 기반 공격 흐름(방어 관점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>시나리오</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>제목</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>전술</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>세부위협</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>행위(근거 사고)</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>탐지·차단 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>ESN-01</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>엣지 VPN 0-day → LotL 정찰·자격증명 → 원격 서비스 확산(사람 운영 침투)</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>초기 침투</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>ENT-IA-01</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>인터넷 노출 엣지 VPN의 연쇄 0-day로 경계 안 진입(ENI-006)</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>엣지 장비 취약점 공개·악용 동향 대조와 비정상 세션 모니터링</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>ESN-01</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>엣지 VPN 0-day → LotL 정찰·자격증명 → 원격 서비스 확산(사람 운영 침투)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>실행</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>ENT-EX-01.1, ENT-EX-03, ENT-DI-01, ENT-DI-02</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>PowerShell·정상 바이너리(LotL)로 실행하고 호스트·AD를 열거(ENI-001)</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>스크립트 로깅과 짧은 시간의 연쇄 탐색·LotL 실행을 행위 기반으로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>ESN-01</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>엣지 VPN 0-day → LotL 정찰·자격증명 → 원격 서비스 확산(사람 운영 침투)</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 접근</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>ENT-CA-01.1, ENT-LM-01</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>LSASS 덤프로 자격증명을 얻어 원격 서비스로 확산(ENI-012)</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>LSASS 비정상 접근과 비정상 원격 세션을 EDR·네트워크로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>ESN-02</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>사람 운영 랜섬웨어 — 초기 침투 → EDR 무력화(BYOVD) → 복구 방해 → 암호화·갈취</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>초기 침투</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>ENT-IA-02</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>MFA 미적용 VPN으로 정상 로그인해 진입(ENI-014)</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>원격 로그인 이상·MFA 미적용 경로를 아이덴티티 기반으로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>ESN-02</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>사람 운영 랜섬웨어 — 초기 침투 → EDR 무력화(BYOVD) → 복구 방해 → 암호화·갈취</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 접근</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>ENT-CA-01.1, ENT-DI-02, ENT-LM-01</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 탈취·AD 열거 후 원격 서비스로 도메인 확산(ENI-012)</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>LSASS 접근·AD 열거·비정상 원격 세션 상관 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>ESN-02</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>사람 운영 랜섬웨어 — 초기 침투 → EDR 무력화(BYOVD) → 복구 방해 → 암호화·갈취</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>방어 회피</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>ENT-DE-01.1, ENT-PV-04</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>서명된 취약 드라이버로 EDR을 커널에서 무력화(ENI-016)</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>보안 서비스 중지·드라이버 로드와 EDR 텔레메트리 단절 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>ESN-02</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>사람 운영 랜섬웨어 — 초기 침투 → EDR 무력화(BYOVD) → 복구 방해 → 암호화·갈취</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>영향</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>ENT-IM-02, ENT-IM-01</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>섀도 카피·백업을 지운 뒤 전사 암호화(ENI-015)</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>섀도 카피 삭제·대량 암호화 행위를 행위 기반으로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>ESN-03</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>파일전송 엣지 0-day → 대량 데이터 반출 → 유출 협박 갈취(Cl0p 패턴)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>초기 침투</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>ENT-IA-01</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>노출 파일전송 장비의 공개 전 취약점으로 진입(ENI-004)</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>파일전송 장비 취약점 동향 대조와 비정상 접근 모니터링</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>ESN-03</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>파일전송 엣지 0-day → 대량 데이터 반출 → 유출 협박 갈취(Cl0p 패턴)</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>반출</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>ENT-EF-02</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>파일전송 솔루션에서 데이터를 대량 반출(ENI-010)</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>대량 업로드·외부 전송을 네트워크·DLP 기반으로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>ESN-03</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>파일전송 엣지 0-day → 대량 데이터 반출 → 유출 협박 갈취(Cl0p 패턴)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>영향</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ENT-IM-05</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>유출 데이터 공개 협박으로 갈취(ENI-004)</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>대량 반출 선행 징후와 갈취 정황을 통합 모니터링</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>ESN-04</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>원격 서비스 취약점 웜 확산 → 자격증명 재사용 → 파괴·암호화</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>측면 이동</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ENT-LM-04</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>원격 서비스 취약점으로 패치되지 않은 호스트에 자동 확산(ENI-022)</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>내부 취약 서비스 악용 시도·급격한 횡적 전파를 네트워크로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>ESN-04</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>원격 서비스 취약점 웜 확산 → 자격증명 재사용 → 파괴·암호화</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 접근</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ENT-CA-01.1, ENT-LM-02</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>자격증명을 탈취·재사용해 추가 확산(ENI-021)</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>비정상 티켓·해시 사용과 로그온 유형 불일치 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>ESN-04</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>원격 서비스 취약점 웜 확산 → 자격증명 재사용 → 파괴·암호화</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>영향</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ENT-IM-03</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>디스크를 파괴해 운영 중단(ENI-021)</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>대량 삭제·MBR 변조 행위를 행위 기반으로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>ESN-05</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>비콘 C2 — 프로세스 인젝션 → 암호화·도메인 프런팅 C2 → 반출</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>권한 상승</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ENT-PV-01.1</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>비콘이 프로세스 인젝션으로 메모리에서 실행(ENI-018)</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>원격 스레드 생성·메모리 실행을 EDR로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>ESN-05</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>비콘 C2 — 프로세스 인젝션 → 암호화·도메인 프런팅 C2 → 반출</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>명령·제어</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>ENT-C2-01.2, ENT-C2-04</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>HTTPS·도메인 프런팅으로 암호화 C2 유지(ENI-018)</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>비컨 주기·SNI 불일치·목적지 평판을 네트워크로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>ESN-05</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>비콘 C2 — 프로세스 인젝션 → 암호화·도메인 프런팅 C2 → 반출</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>반출</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ENT-CO-02, ENT-EF-01</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>데이터를 압축·암호화 스테이징 후 C2 채널로 반출(ENI-031)</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>대용량 스테이징과 C2 업로드량 전환을 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>ESN-06</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>신뢰 관계(MSP·원격 관리) 경유 → 하위 고객 대량 랜섬웨어</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>초기 침투</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>ENT-IA-05</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>원격 관리 플랫폼 취약점을 경유해 하위 고객 환경에 접근(ENI-011)</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>관리 도구발 대량·일괄 작업과 신뢰 계정 이상 사용을 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>ESN-06</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>신뢰 관계(MSP·원격 관리) 경유 → 하위 고객 대량 랜섬웨어</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>영향</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>ENT-IM-01</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>신뢰된 원격 관리 경로로 랜섬웨어를 일괄 배포(ENI-009)</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>대량 암호화 행위와 배포 경로 이상을 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>ESN-07</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>지표 삭제·위장·난독화로 사후 분석 방해(은닉 보조 흐름)</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>방어 회피</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>ENT-DE-05, ENT-DE-04</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>페이로드를 난독화하고 정상 이름·경로로 위장(ENI-033)</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>경로·서명 불일치와 비정상 인코딩을 무결성·행위 기반으로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>ESN-07</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>지표 삭제·위장·난독화로 사후 분석 방해(은닉 보조 흐름)</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>방어 회피</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>ENT-DE-03</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>이벤트 로그를 지워 탐지·분석을 무력화(ENI-001)</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>로그 삭제·감사 정책 변경과 원격 수집 로그 공백을 모니터링</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>ESN-08</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>커널·펌웨어 하위 계층 은닉 — 루트킷·부트킷으로 장기 잠복</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>방어 회피</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>ENT-DE-07</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>커널 루트킷으로 프로세스·연결을 숨기며 장기 잠복(ENI-025)</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>커널 무결성·드라이버 서명과 메모리 무결성 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>ESN-08</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>커널·펌웨어 하위 계층 은닉 — 루트킷·부트킷으로 장기 잠복</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>방어 회피</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>ENT-DE-08</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>UEFI 부트킷·펌웨어 임플란트로 재설치에도 지속(ENI-024)</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>보안 부팅·측정 부팅과 펌웨어 해시 변화 점검</t>
         </is>
       </c>
     </row>
